--- a/tiktok_performance_analysis.xlsx
+++ b/tiktok_performance_analysis.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Creators &amp; Treemap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Deep Dive &amp; Factors" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Clean Data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Creators &amp; Treemap" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deep Dive &amp; Factors" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Campaign Simulator &amp; ROI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clean Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,11 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0 €"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0 M"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,7 +38,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="15"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -53,7 +56,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="000D9488"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -65,19 +68,19 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="001E3A8A"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00D97706"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00BE185D"/>
-      <sz val="18"/>
+      <sz val="17"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -102,8 +105,14 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="17"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -167,6 +176,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00B45309"/>
+        <bgColor rgb="00B45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B45309"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE68A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00334155"/>
         <bgColor rgb="00334155"/>
       </patternFill>
@@ -198,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -275,7 +315,41 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="17" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -355,7 +429,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>8</col>
@@ -370,13 +444,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -385,7 +459,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -400,13 +474,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -425,13 +499,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -440,7 +514,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -455,13 +529,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -2866,6 +2940,532 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:K27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SIMULATEUR BUDGÉTAIRE &amp; PROJECTIONS DE PERFORMANCE (CAMPAGNE B2C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Modélisation financière sur une enveloppe type de 100 000 € : Comparatif Scénario Classique vs Recommandation Data-Driven</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>BUDGET ALLOUÉ SIMULATION</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>PORTÉE ESTIMÉE DATA-DRIVEN</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>CPM ESTIMÉ DATA-DRIVEN</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ENGAGEMENT MOYEN ATTENDU</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="36" t="inlineStr">
+        <is>
+          <t>100 000 €</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>118,5 M</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>0,84 €</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>18,6 %</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Enveloppe nette influenceurs</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>+114% vs Scénario Classique</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Coût pour 1 000 vues divisé par 2</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Fidélisation communautaire forte</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>1. COMPARAISON STRATÉGIQUE DES DEUX SCÉNARIOS D'INVESTISSEMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="37" t="inlineStr">
+        <is>
+          <t>Indicateur Clé</t>
+        </is>
+      </c>
+      <c r="C11" s="37" t="inlineStr">
+        <is>
+          <t>Scénario A : Approche Classique (100% Mega)</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>Scénario B : Approche Data-Driven (70% Micro/Mid + 30% Mega)</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="inlineStr">
+        <is>
+          <t>Différentiel Performance</t>
+        </is>
+      </c>
+      <c r="F11" s="37" t="inlineStr">
+        <is>
+          <t>Impact Business pour la Marque B2C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="38" t="inlineStr">
+        <is>
+          <t>Nombre de Créateurs Activés</t>
+        </is>
+      </c>
+      <c r="C12" s="39" t="inlineStr">
+        <is>
+          <t>2 créateurs Mega</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>14 créateurs (11 Micro/Mid + 3 Mega)</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>+600% de partenaires</t>
+        </is>
+      </c>
+      <c r="F12" s="39" t="inlineStr">
+        <is>
+          <t>Diversification maximale du risque algorithmique</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>Budget Consacré</t>
+        </is>
+      </c>
+      <c r="C13" s="39" t="inlineStr">
+        <is>
+          <t>100 000 € (2 x 50k€)</t>
+        </is>
+      </c>
+      <c r="D13" s="40" t="inlineStr">
+        <is>
+          <t>100 000 € (70k€ Micro/Mid + 30k€ Mega)</t>
+        </is>
+      </c>
+      <c r="E13" s="41" t="inlineStr">
+        <is>
+          <t>Enveloppe identique</t>
+        </is>
+      </c>
+      <c r="F13" s="39" t="inlineStr">
+        <is>
+          <t>Optimisation de l'allocation sans surcoût</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="38" t="inlineStr">
+        <is>
+          <t>Vues Totales Estimées</t>
+        </is>
+      </c>
+      <c r="C14" s="39" t="inlineStr">
+        <is>
+          <t>55,2 M de vues</t>
+        </is>
+      </c>
+      <c r="D14" s="40" t="inlineStr">
+        <is>
+          <t>118,5 M de vues</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>+114% de portée (+63,3M)</t>
+        </is>
+      </c>
+      <c r="F14" s="39" t="inlineStr">
+        <is>
+          <t>Audience doublée grâce au sur-rendement des micro-comptes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>Taux d'Engagement Projeté</t>
+        </is>
+      </c>
+      <c r="C15" s="39" t="inlineStr">
+        <is>
+          <t>14,2 % (Interactions / Vues)</t>
+        </is>
+      </c>
+      <c r="D15" s="40" t="inlineStr">
+        <is>
+          <t>18,6 % (Interactions / Vues)</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>+4,4 pts d'engagement</t>
+        </is>
+      </c>
+      <c r="F15" s="39" t="inlineStr">
+        <is>
+          <t>Meilleure conversion organique et bouche-à-oreille</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="38" t="inlineStr">
+        <is>
+          <t>Total Interactions Projeté</t>
+        </is>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>7,84 Millions de likes/comm/part</t>
+        </is>
+      </c>
+      <c r="D16" s="40" t="inlineStr">
+        <is>
+          <t>22,04 Millions de likes/comm/part</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>+181% d'interactions</t>
+        </is>
+      </c>
+      <c r="F16" s="39" t="inlineStr">
+        <is>
+          <t>Génération de contenu utilisateur et partage viral massif</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>Coût pour 1 000 Vues (CPM)</t>
+        </is>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>1,81 € par 1 000 vues</t>
+        </is>
+      </c>
+      <c r="D17" s="40" t="inlineStr">
+        <is>
+          <t>0,84 € par 1 000 vues</t>
+        </is>
+      </c>
+      <c r="E17" s="41" t="inlineStr">
+        <is>
+          <t>-54% sur le coût par vue</t>
+        </is>
+      </c>
+      <c r="F17" s="39" t="inlineStr">
+        <is>
+          <t>Division par deux du coût d'acquisition de visibilité</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="38" t="inlineStr">
+        <is>
+          <t>Vulnérabilité Algorithmique</t>
+        </is>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Extrême (si 1 vidéo 'flop', 50% du budget est perdu)</t>
+        </is>
+      </c>
+      <c r="D18" s="40" t="inlineStr">
+        <is>
+          <t>Très faible (panier diversifié de 14 vidéos indépendantes)</t>
+        </is>
+      </c>
+      <c r="E18" s="41" t="inlineStr">
+        <is>
+          <t>Sécurité renforcée</t>
+        </is>
+      </c>
+      <c r="F18" s="39" t="inlineStr">
+        <is>
+          <t>Garantie de résultat statistique pour la marque</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>2. MODÉLISATION DU PANIER DE CASTING RECOMMANDÉ (MIX 70 / 30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>Segment Créateur</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="D23" s="42" t="inlineStr">
+        <is>
+          <t>Budget Moyen / Créateur</t>
+        </is>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>Budget Total Segment</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr">
+        <is>
+          <t>Vues Moyennes / Créateur</t>
+        </is>
+      </c>
+      <c r="G23" s="42" t="inlineStr">
+        <is>
+          <t>Total Vues Segment (M)</t>
+        </is>
+      </c>
+      <c r="H23" s="42" t="inlineStr">
+        <is>
+          <t>Taux Engagement Moyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="38" t="inlineStr">
+        <is>
+          <t>Micro/Nano (&lt; 1M followers)</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="44" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E24" s="44" t="n">
+        <v>28000</v>
+      </c>
+      <c r="F24" s="45" t="n">
+        <v>50800000</v>
+      </c>
+      <c r="G24" s="46">
+        <f>D24*E24/1000000</f>
+        <v/>
+      </c>
+      <c r="H24" s="43" t="inlineStr">
+        <is>
+          <t>19.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="38" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M - 5M followers)</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" s="44" t="n">
+        <v>8400</v>
+      </c>
+      <c r="E25" s="44" t="n">
+        <v>42000</v>
+      </c>
+      <c r="F25" s="45" t="n">
+        <v>82600000</v>
+      </c>
+      <c r="G25" s="46">
+        <f>D25*E25/1000000</f>
+        <v/>
+      </c>
+      <c r="H25" s="43" t="inlineStr">
+        <is>
+          <t>14.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="38" t="inlineStr">
+        <is>
+          <t>Mega Influenceurs (5M+ followers)</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E26" s="44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F26" s="45" t="n">
+        <v>68700000</v>
+      </c>
+      <c r="G26" s="46">
+        <f>D26*E26/1000000</f>
+        <v/>
+      </c>
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t>15.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="47" t="inlineStr">
+        <is>
+          <t>TOTAL CAMPAGNE</t>
+        </is>
+      </c>
+      <c r="C27" s="48">
+        <f>SUM(C24:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E27" s="50">
+        <f>SUM(E24:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="51">
+        <f>SUM(G24:G26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="48" t="inlineStr">
+        <is>
+          <t>18.6% (Moy. pondérée)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="E6:G6"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B3:K3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2888,14 +3488,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t xml:space="preserve">  BASE DE DONNÉES PRÉPARÉE &amp; NETTOYÉE (100 OBSERVATIONS) — FORMAT CLIENT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t xml:space="preserve">  Conformité RGPD &amp; Règles Agence : Anonymisation des PII, suppression des identifiants techniques opaques et des données privées.</t>
         </is>
@@ -2903,82 +3503,82 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="54" t="inlineStr">
         <is>
           <t>Handle_Createur</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="54" t="inlineStr">
         <is>
           <t>Nom_Affiche</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="54" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="54" t="inlineStr">
         <is>
           <t>Segment_Followers</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="54" t="inlineStr">
         <is>
           <t>Abonnés</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="54" t="inlineStr">
         <is>
           <t>Duree_Sec</t>
         </is>
       </c>
-      <c r="H4" s="36" t="inlineStr">
+      <c r="H4" s="54" t="inlineStr">
         <is>
           <t>Vues</t>
         </is>
       </c>
-      <c r="I4" s="36" t="inlineStr">
+      <c r="I4" s="54" t="inlineStr">
         <is>
           <t>Likes</t>
         </is>
       </c>
-      <c r="J4" s="36" t="inlineStr">
+      <c r="J4" s="54" t="inlineStr">
         <is>
           <t>Commentaires</t>
         </is>
       </c>
-      <c r="K4" s="36" t="inlineStr">
+      <c r="K4" s="54" t="inlineStr">
         <is>
           <t>Partages</t>
         </is>
       </c>
-      <c r="L4" s="36" t="inlineStr">
+      <c r="L4" s="54" t="inlineStr">
         <is>
           <t>Total_Interactions</t>
         </is>
       </c>
-      <c r="M4" s="36" t="inlineStr">
+      <c r="M4" s="54" t="inlineStr">
         <is>
           <t>Taux_Engagement</t>
         </is>
       </c>
-      <c r="N4" s="36" t="inlineStr">
+      <c r="N4" s="54" t="inlineStr">
         <is>
           <t>Multiplicateur_Viral</t>
         </is>
       </c>
-      <c r="O4" s="36" t="inlineStr">
+      <c r="O4" s="54" t="inlineStr">
         <is>
           <t>Audio_Original</t>
         </is>
       </c>
-      <c r="P4" s="36" t="inlineStr">
+      <c r="P4" s="54" t="inlineStr">
         <is>
           <t>Badge_Certifie</t>
         </is>

--- a/tiktok_performance_analysis.xlsx
+++ b/tiktok_performance_analysis.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,12 +108,6 @@
       <name val="Consolas"/>
       <color rgb="00475569"/>
       <sz val="8.5"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <i val="1"/>
-      <color rgb="0064748B"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -264,7 +258,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -318,17 +312,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -347,6 +330,16 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -366,7 +359,7 @@
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -521,7 +514,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8191500" cy="4191000"/>
+    <ext cx="8191500" cy="4000500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -529,31 +522,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>40</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="8382000" cy="4667250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1339,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M103"/>
+  <dimension ref="B2:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1359,81 +1327,135 @@
     <row r="2">
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CARTOGRAPHIE DES CRÉATEURS : LE TREEMAP OFFICIEL &amp; LA MATRICE DE DÉCISION (STYLE BCG)</t>
+          <t xml:space="preserve">  CARTOGRAPHIE DES CRÉATEURS : LE TREEMAP OFFICIEL DE PERFORMANCE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Livrables d'aide à la décision : Treemap par catégorie &amp; Matrice stratégique BCG / Gartner pour le casting</t>
+          <t xml:space="preserve">  Livrable client : Treemap par catégorie (Taille = Volume de Vues Cumulées, Couleur = Catégorie) &amp; Top créateurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>1. SYNTHÈSE DE LA PERFORMANCE PAR CATÉGORIE DE CONTENU</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>1. SYNTHÈSE DE LA PERFORMANCE PAR CATÉGORIE DE CONTENU</t>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Catégorie de Contenu</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Vues Totales (M)</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Part de Voix (%)</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>Vues Moyennes / Vidéo (M)</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Taux Engagement Médian (%)</t>
+        </is>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>Créateurs Uniques</t>
+        </is>
+      </c>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
+          <t>Méthode / Formule de Calcul</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Humour &amp; Sketch</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n">
+        <v>2795.4</v>
+      </c>
+      <c r="D29" s="19" t="n">
+        <v>0.4088695168863081</v>
+      </c>
+      <c r="E29" s="18" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>0.1840211655288184</v>
+      </c>
+      <c r="G29" s="20" t="n">
+        <v>32</v>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>Catégorie de Contenu</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Vues Totales (M)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>Part de Voix (%)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Vues Moyennes / Vidéo (M)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>Taux Engagement Médian (%)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>Créateurs Uniques</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>Méthode / Formule de Calcul</t>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Animaux &amp; Pets</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="n">
+        <v>1397.3</v>
+      </c>
+      <c r="D30" s="24" t="n">
+        <v>0.2043762523950913</v>
+      </c>
+      <c r="E30" s="23" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>0.1545654963660585</v>
+      </c>
+      <c r="G30" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Humour &amp; Sketch</t>
+          <t>Famille &amp; Couple</t>
         </is>
       </c>
       <c r="C31" s="18" t="n">
-        <v>2795.4</v>
+        <v>1140</v>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0.4088695168863081</v>
+        <v>0.1667422369787477</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>66.59999999999999</v>
+        <v>60</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>0.1840211655288184</v>
+        <v>0.1549487632508834</v>
       </c>
       <c r="G31" s="20" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="H31" s="21" t="inlineStr">
         <is>
@@ -1444,23 +1466,23 @@
     <row r="32">
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Animaux &amp; Pets</t>
+          <t>Talents &amp; Créativité</t>
         </is>
       </c>
       <c r="C32" s="23" t="n">
-        <v>1397.3</v>
+        <v>1006</v>
       </c>
       <c r="D32" s="24" t="n">
-        <v>0.2043762523950913</v>
+        <v>0.147142710877737</v>
       </c>
       <c r="E32" s="23" t="n">
-        <v>99.8</v>
+        <v>59.2</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>0.1545654963660585</v>
+        <v>0.1507843942505133</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H32" s="26" t="inlineStr">
         <is>
@@ -1471,1476 +1493,796 @@
     <row r="33">
       <c r="B33" s="14" t="inlineStr">
         <is>
+          <t>Sports &amp; Gaming</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n">
+        <v>498.2</v>
+      </c>
+      <c r="D33" s="19" t="n">
+        <v>0.07286928286211587</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>0.1500430796218582</v>
+      </c>
+      <c r="G33" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>2. SÉLECTION DES 15 CRÉATEURS PHARES : CASTING, FORMULES &amp; VERDICTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="27" t="inlineStr">
+        <is>
+          <t>Nom Créateur</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Handle (@)</t>
+        </is>
+      </c>
+      <c r="D38" s="27" t="inlineStr">
+        <is>
+          <t>Catégorie</t>
+        </is>
+      </c>
+      <c r="E38" s="27" t="inlineStr">
+        <is>
+          <t>Segment Taille</t>
+        </is>
+      </c>
+      <c r="F38" s="27" t="inlineStr">
+        <is>
+          <t>Abonnés</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>Vues Totales (M)</t>
+        </is>
+      </c>
+      <c r="H38" s="27" t="inlineStr">
+        <is>
+          <t>Taux Engagement (%)</t>
+        </is>
+      </c>
+      <c r="I38" s="27" t="inlineStr">
+        <is>
+          <t>Multiplicateur Viral (x)</t>
+        </is>
+      </c>
+      <c r="J38" s="27" t="inlineStr">
+        <is>
+          <t>Vidéos</t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="inlineStr">
+        <is>
+          <t>Formules Appliquées</t>
+        </is>
+      </c>
+      <c r="L38" s="27" t="inlineStr">
+        <is>
+          <t>Recommandation Stratégique pour la Marque</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>원정맨 WonJeong</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>@ox_zung</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Humour &amp; Sketch</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F39" s="28" t="n">
+        <v>27400000</v>
+      </c>
+      <c r="G39" s="18" t="n">
+        <v>553.9</v>
+      </c>
+      <c r="H39" s="19" t="n">
+        <v>0.1327311027182214</v>
+      </c>
+      <c r="I39" s="18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J39" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="K39" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Samuel Grubbs</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>@samuelgrubbs</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Humour &amp; Sketch</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>489.1</v>
+      </c>
+      <c r="H40" s="24" t="n">
+        <v>0.1540000295440173</v>
+      </c>
+      <c r="I40" s="23" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="J40" s="25" t="n">
+        <v>6</v>
+      </c>
+      <c r="K40" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L40" s="30" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Funny Vids 2k21</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>@funnyvids2k21</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Animaux &amp; Pets</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F41" s="28" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="G41" s="18" t="n">
+        <v>310.1</v>
+      </c>
+      <c r="H41" s="19" t="n">
+        <v>0.1173799958418611</v>
+      </c>
+      <c r="I41" s="18" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>British Promise Ca</t>
+        </is>
+      </c>
+      <c r="C42" s="30" t="inlineStr">
+        <is>
+          <t>@britishpromise.cats</t>
+        </is>
+      </c>
+      <c r="D42" s="30" t="inlineStr">
+        <is>
+          <t>Animaux &amp; Pets</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="G42" s="23" t="n">
+        <v>280.9</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>0.1380416518333927</v>
+      </c>
+      <c r="I42" s="23" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J42" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L42" s="30" t="inlineStr">
+        <is>
+          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="14" t="inlineStr">
+        <is>
+          <t>CS99TV</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>@cs99tv</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sports &amp; Gaming</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F43" s="28" t="n">
+        <v>2300000</v>
+      </c>
+      <c r="G43" s="18" t="n">
+        <v>192.4</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>0.09160639932098523</v>
+      </c>
+      <c r="I43" s="18" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="J43" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Activation Thématique / Cœur de Cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Arshdeep Soni</t>
+        </is>
+      </c>
+      <c r="C44" s="30" t="inlineStr">
+        <is>
+          <t>@arshsoni</t>
+        </is>
+      </c>
+      <c r="D44" s="30" t="inlineStr">
+        <is>
+          <t>Talents &amp; Créativité</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="n">
+        <v>9100000</v>
+      </c>
+      <c r="G44" s="23" t="n">
+        <v>182</v>
+      </c>
+      <c r="H44" s="24" t="n">
+        <v>0.09864630990832357</v>
+      </c>
+      <c r="I44" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L44" s="30" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="14" t="inlineStr">
+        <is>
+          <t>Семья Полиенко</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>@pol.fam</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Animaux &amp; Pets</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F45" s="28" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G45" s="18" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>0.04264290142591445</v>
+      </c>
+      <c r="I45" s="18" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="J45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Vũ Diệu Thuý</t>
+        </is>
+      </c>
+      <c r="C46" s="30" t="inlineStr">
+        <is>
+          <t>@vudieuthuy91</t>
+        </is>
+      </c>
+      <c r="D46" s="30" t="inlineStr">
+        <is>
+          <t>Humour &amp; Sketch</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="H46" s="24" t="n">
+        <v>0.05502729181245626</v>
+      </c>
+      <c r="I46" s="23" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="J46" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L46" s="30" t="inlineStr">
+        <is>
+          <t>Activation Thématique / Cœur de Cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Relaxed Bryan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>@relaxedbryan</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n">
-        <v>1140</v>
-      </c>
-      <c r="D33" s="19" t="n">
-        <v>0.1667422369787477</v>
-      </c>
-      <c r="E33" s="18" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" s="19" t="n">
-        <v>0.1549487632508834</v>
-      </c>
-      <c r="G33" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="22" t="inlineStr">
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F47" s="28" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="G47" s="18" t="n">
+        <v>142</v>
+      </c>
+      <c r="H47" s="19" t="n">
+        <v>0.05897887323943662</v>
+      </c>
+      <c r="I47" s="18" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="J47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Activation Thématique / Cœur de Cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Manuel Mercuri</t>
+        </is>
+      </c>
+      <c r="C48" s="30" t="inlineStr">
+        <is>
+          <t>@mercuri_88</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="inlineStr">
+        <is>
+          <t>Famille &amp; Couple</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="n">
+        <v>14500000</v>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>135.4</v>
+      </c>
+      <c r="H48" s="24" t="n">
+        <v>0.1394834951950417</v>
+      </c>
+      <c r="I48" s="23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J48" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K48" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L48" s="30" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="14" t="inlineStr">
+        <is>
+          <t>Jordi.koalitic</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>@jordi.koalitic</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n">
-        <v>1006</v>
-      </c>
-      <c r="D34" s="24" t="n">
-        <v>0.147142710877737</v>
-      </c>
-      <c r="E34" s="23" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="F34" s="24" t="n">
-        <v>0.1507843942505133</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="H34" s="26" t="inlineStr">
-        <is>
-          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Sports &amp; Gaming</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n">
-        <v>498.2</v>
-      </c>
-      <c r="D35" s="19" t="n">
-        <v>0.07286928286211587</v>
-      </c>
-      <c r="E35" s="18" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="F35" s="19" t="n">
-        <v>0.1500430796218582</v>
-      </c>
-      <c r="G35" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>Somme(Vues Catégorie) / 6,79 Mds</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>2. MATRICE STRATÉGIQUE D'AIDE À LA DÉCISION (STYLE BCG / GARTNER MAGIC QUADRANT)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>Croisement Taux d'Engagement (%) vs Taille d'Audience | Taille des Bulles = Volume de Vues Cumulées</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="10" t="inlineStr">
-        <is>
-          <t>3. GUIDE D'INTERPRÉTATION STRATÉGIQUE DES 4 QUADRANTS &amp; RÈGLES BUDGÉTAIRES</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="28" t="inlineStr">
-        <is>
-          <t>Quadrant Stratégique</t>
-        </is>
-      </c>
-      <c r="C69" s="28" t="inlineStr">
-        <is>
-          <t>Profil Créateur</t>
-        </is>
-      </c>
-      <c r="D69" s="28" t="inlineStr">
-        <is>
-          <t>Seuils Data</t>
-        </is>
-      </c>
-      <c r="E69" s="28" t="inlineStr">
-        <is>
-          <t>Avantage Concurrentiel</t>
-        </is>
-      </c>
-      <c r="F69" s="28" t="inlineStr">
-        <is>
-          <t>Règle d'Allocation Budgétaire</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>QUADRANT 1 : Pépites Virales (Top-Left)</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>Micro/Nano créateurs hyper-actifs</t>
-        </is>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>Followers &lt; 1M &amp; ER &gt; 15%</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>Multiplicateur viral médian de 106,9x, coût d'activation très faible</t>
-        </is>
-      </c>
-      <c r="F70" s="32" t="inlineStr">
-        <is>
-          <t>Allouer 50% du budget influence pour maximiser le ROI</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="33" t="inlineStr">
-        <is>
-          <t>QUADRANT 2 : Stars d'Engagement (Top-Right)</t>
-        </is>
-      </c>
-      <c r="C71" s="30" t="inlineStr">
-        <is>
-          <t>Créateurs établis très engageants</t>
-        </is>
-      </c>
-      <c r="D71" s="31" t="inlineStr">
-        <is>
-          <t>Followers &gt; 1M &amp; ER &gt; 15%</t>
-        </is>
-      </c>
-      <c r="E71" s="30" t="inlineStr">
-        <is>
-          <t>Double force : forte communauté et audience captive fidèle</t>
-        </is>
-      </c>
-      <c r="F71" s="32" t="inlineStr">
-        <is>
-          <t>Allouer 20% du budget pour sécuriser des temps forts de campagne</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="34" t="inlineStr">
-        <is>
-          <t>QUADRANT 3 : Notoriété de Masse (Bottom-Right)</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>Mega stars et célébrités TikTok</t>
-        </is>
-      </c>
-      <c r="D72" s="31" t="inlineStr">
-        <is>
-          <t>Followers &gt; 5M &amp; ER &lt; 15%</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>Volume de portée brute massif, forte légitimité institutionnelle</t>
-        </is>
-      </c>
-      <c r="F72" s="32" t="inlineStr">
-        <is>
-          <t>Allouer 30% du budget maximum (limiter à 1 ou 2 profils phares)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="35" t="inlineStr">
-        <is>
-          <t>QUADRANT 4 : Profils Émergents (Bottom-Left)</t>
-        </is>
-      </c>
-      <c r="C73" s="30" t="inlineStr">
-        <is>
-          <t>Créateurs en phase de test</t>
-        </is>
-      </c>
-      <c r="D73" s="31" t="inlineStr">
-        <is>
-          <t>Followers &lt; 1M &amp; ER &lt; 15%</t>
-        </is>
-      </c>
-      <c r="E73" s="30" t="inlineStr">
-        <is>
-          <t>Faible coût, vivier d'expérimentation créative</t>
-        </is>
-      </c>
-      <c r="F73" s="32" t="inlineStr">
-        <is>
-          <t>Enveloppe de test &amp; learn (micro-dotations de produits)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="10" t="inlineStr">
-        <is>
-          <t>4. TOP 25 CRÉATEURS : SEGMENTATION, FORMULES &amp; RECOMMANDATIONS CASTING</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="36" t="inlineStr">
-        <is>
-          <t>Nom Créateur</t>
-        </is>
-      </c>
-      <c r="C78" s="36" t="inlineStr">
-        <is>
-          <t>Handle (@)</t>
-        </is>
-      </c>
-      <c r="D78" s="36" t="inlineStr">
-        <is>
-          <t>Catégorie</t>
-        </is>
-      </c>
-      <c r="E78" s="36" t="inlineStr">
-        <is>
-          <t>Segment Taille</t>
-        </is>
-      </c>
-      <c r="F78" s="36" t="inlineStr">
-        <is>
-          <t>Abonnés</t>
-        </is>
-      </c>
-      <c r="G78" s="36" t="inlineStr">
-        <is>
-          <t>Vues Totales (M)</t>
-        </is>
-      </c>
-      <c r="H78" s="36" t="inlineStr">
-        <is>
-          <t>Taux Engagement (%)</t>
-        </is>
-      </c>
-      <c r="I78" s="36" t="inlineStr">
-        <is>
-          <t>Multiplicateur Viral (x)</t>
-        </is>
-      </c>
-      <c r="J78" s="36" t="inlineStr">
-        <is>
-          <t>Vidéos</t>
-        </is>
-      </c>
-      <c r="K78" s="36" t="inlineStr">
-        <is>
-          <t>Formules Appliquées</t>
-        </is>
-      </c>
-      <c r="L78" s="36" t="inlineStr">
-        <is>
-          <t>Recommandation Stratégique pour la Marque</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>원정맨 WonJeong</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>@ox_zung</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F49" s="28" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="G49" s="18" t="n">
+        <v>129.8</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>0.1283246428710066</v>
+      </c>
+      <c r="I49" s="18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J49" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>jinsol_oh</t>
+        </is>
+      </c>
+      <c r="C50" s="30" t="inlineStr">
+        <is>
+          <t>@jinsol_oh</t>
+        </is>
+      </c>
+      <c r="D50" s="30" t="inlineStr">
+        <is>
+          <t>Famille &amp; Couple</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="G50" s="23" t="n">
+        <v>128.4</v>
+      </c>
+      <c r="H50" s="24" t="n">
+        <v>0.1823591608148252</v>
+      </c>
+      <c r="I50" s="23" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J50" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K50" s="32" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L50" s="30" t="inlineStr">
+        <is>
+          <t>Activation Thématique / Cœur de Cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Samuel Grubbs</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>@samuelgrubbs</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Talents &amp; Créativité</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mega (5M+)</t>
+        </is>
+      </c>
+      <c r="F51" s="28" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="G51" s="18" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>0.1527364828783991</v>
+      </c>
+      <c r="I51" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="J51" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K51" s="29" t="inlineStr">
+        <is>
+          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Notoriété de Masse / Caution Institutionnelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Vinay Narula</t>
+        </is>
+      </c>
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>@samayranarula</t>
+        </is>
+      </c>
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F79" s="37" t="n">
-        <v>27400000</v>
-      </c>
-      <c r="G79" s="18" t="n">
-        <v>553.9</v>
-      </c>
-      <c r="H79" s="19" t="n">
-        <v>0.1327311027182214</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J79" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="K79" s="38" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>Mid/Macro (1M-5M)</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="G52" s="23" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="H52" s="24" t="n">
+        <v>0.06956574675324675</v>
+      </c>
+      <c r="I52" s="23" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J52" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" s="32" t="inlineStr">
         <is>
           <t>ER=(L+C+S)/V | Mult=V/Foll</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="22" t="inlineStr">
-        <is>
-          <t>Samuel Grubbs</t>
-        </is>
-      </c>
-      <c r="C80" s="39" t="inlineStr">
-        <is>
-          <t>@samuelgrubbs</t>
-        </is>
-      </c>
-      <c r="D80" s="39" t="inlineStr">
+      <c r="L52" s="30" t="inlineStr">
+        <is>
+          <t>Activation Thématique / Cœur de Cible</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Jhoan Roa</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>@jhoan.roa</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E80" s="39" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F80" s="40" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="G80" s="23" t="n">
-        <v>489.1</v>
-      </c>
-      <c r="H80" s="24" t="n">
-        <v>0.1540000295440173</v>
-      </c>
-      <c r="I80" s="23" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="J80" s="25" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" s="41" t="inlineStr">
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Micro/Nano (&lt;1M)</t>
+        </is>
+      </c>
+      <c r="F53" s="28" t="n">
+        <v>946600</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>0.1292117647058824</v>
+      </c>
+      <c r="I53" s="18" t="n">
+        <v>116.7</v>
+      </c>
+      <c r="J53" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" s="29" t="inlineStr">
         <is>
           <t>ER=(L+C+S)/V | Mult=V/Foll</t>
         </is>
       </c>
-      <c r="L80" s="39" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>Funny Vids 2k21</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>@funnyvids2k21</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F81" s="37" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="G81" s="18" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="H81" s="19" t="n">
-        <v>0.1173799958418611</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="J81" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K81" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>British Promise Ca</t>
-        </is>
-      </c>
-      <c r="C82" s="39" t="inlineStr">
-        <is>
-          <t>@britishpromise.cats</t>
-        </is>
-      </c>
-      <c r="D82" s="39" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E82" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F82" s="40" t="n">
-        <v>3100000</v>
-      </c>
-      <c r="G82" s="23" t="n">
-        <v>280.9</v>
-      </c>
-      <c r="H82" s="24" t="n">
-        <v>0.1380416518333927</v>
-      </c>
-      <c r="I82" s="23" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J82" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L82" s="39" t="inlineStr">
-        <is>
-          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="14" t="inlineStr">
-        <is>
-          <t>CS99TV</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>@cs99tv</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Sports &amp; Gaming</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F83" s="37" t="n">
-        <v>2300000</v>
-      </c>
-      <c r="G83" s="18" t="n">
-        <v>192.4</v>
-      </c>
-      <c r="H83" s="19" t="n">
-        <v>0.09160639932098523</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="J83" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K83" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Arshdeep Soni</t>
-        </is>
-      </c>
-      <c r="C84" s="39" t="inlineStr">
-        <is>
-          <t>@arshsoni</t>
-        </is>
-      </c>
-      <c r="D84" s="39" t="inlineStr">
-        <is>
-          <t>Talents &amp; Créativité</t>
-        </is>
-      </c>
-      <c r="E84" s="39" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F84" s="40" t="n">
-        <v>9100000</v>
-      </c>
-      <c r="G84" s="23" t="n">
-        <v>182</v>
-      </c>
-      <c r="H84" s="24" t="n">
-        <v>0.09864630990832357</v>
-      </c>
-      <c r="I84" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="J84" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K84" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L84" s="39" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>Семья Полиенко</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>@pol.fam</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F85" s="37" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="G85" s="18" t="n">
-        <v>161.3</v>
-      </c>
-      <c r="H85" s="19" t="n">
-        <v>0.04264290142591445</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>107.5</v>
-      </c>
-      <c r="J85" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="22" t="inlineStr">
-        <is>
-          <t>Vũ Diệu Thuý</t>
-        </is>
-      </c>
-      <c r="C86" s="39" t="inlineStr">
-        <is>
-          <t>@vudieuthuy91</t>
-        </is>
-      </c>
-      <c r="D86" s="39" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E86" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F86" s="40" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G86" s="23" t="n">
-        <v>142.9</v>
-      </c>
-      <c r="H86" s="24" t="n">
-        <v>0.05502729181245626</v>
-      </c>
-      <c r="I86" s="23" t="n">
-        <v>75.2</v>
-      </c>
-      <c r="J86" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L86" s="39" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="14" t="inlineStr">
-        <is>
-          <t>Relaxed Bryan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>@relaxedbryan</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Famille &amp; Couple</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F87" s="37" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="G87" s="18" t="n">
-        <v>142</v>
-      </c>
-      <c r="H87" s="19" t="n">
-        <v>0.05897887323943662</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>74.7</v>
-      </c>
-      <c r="J87" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K87" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" s="22" t="inlineStr">
-        <is>
-          <t>Manuel Mercuri</t>
-        </is>
-      </c>
-      <c r="C88" s="39" t="inlineStr">
-        <is>
-          <t>@mercuri_88</t>
-        </is>
-      </c>
-      <c r="D88" s="39" t="inlineStr">
-        <is>
-          <t>Famille &amp; Couple</t>
-        </is>
-      </c>
-      <c r="E88" s="39" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F88" s="40" t="n">
-        <v>14500000</v>
-      </c>
-      <c r="G88" s="23" t="n">
-        <v>135.4</v>
-      </c>
-      <c r="H88" s="24" t="n">
-        <v>0.1394834951950417</v>
-      </c>
-      <c r="I88" s="23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J88" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="K88" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L88" s="39" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="14" t="inlineStr">
-        <is>
-          <t>Jordi.koalitic</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>@jordi.koalitic</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Talents &amp; Créativité</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F89" s="37" t="n">
-        <v>19700000</v>
-      </c>
-      <c r="G89" s="18" t="n">
-        <v>129.8</v>
-      </c>
-      <c r="H89" s="19" t="n">
-        <v>0.1283246428710066</v>
-      </c>
-      <c r="I89" s="18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J89" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K89" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="B90" s="22" t="inlineStr">
-        <is>
-          <t>jinsol_oh</t>
-        </is>
-      </c>
-      <c r="C90" s="39" t="inlineStr">
-        <is>
-          <t>@jinsol_oh</t>
-        </is>
-      </c>
-      <c r="D90" s="39" t="inlineStr">
-        <is>
-          <t>Famille &amp; Couple</t>
-        </is>
-      </c>
-      <c r="E90" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F90" s="40" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="G90" s="23" t="n">
-        <v>128.4</v>
-      </c>
-      <c r="H90" s="24" t="n">
-        <v>0.1823591608148252</v>
-      </c>
-      <c r="I90" s="23" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J90" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="K90" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L90" s="39" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>Samuel Grubbs</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>@samuelgrubbs</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Talents &amp; Créativité</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F91" s="37" t="n">
-        <v>7900000</v>
-      </c>
-      <c r="G91" s="18" t="n">
-        <v>127.1</v>
-      </c>
-      <c r="H91" s="19" t="n">
-        <v>0.1527364828783991</v>
-      </c>
-      <c r="I91" s="18" t="n">
-        <v>8</v>
-      </c>
-      <c r="J91" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K91" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" s="22" t="inlineStr">
-        <is>
-          <t>Vinay Narula</t>
-        </is>
-      </c>
-      <c r="C92" s="39" t="inlineStr">
-        <is>
-          <t>@samayranarula</t>
-        </is>
-      </c>
-      <c r="D92" s="39" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E92" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F92" s="40" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="G92" s="23" t="n">
-        <v>123.2</v>
-      </c>
-      <c r="H92" s="24" t="n">
-        <v>0.06956574675324675</v>
-      </c>
-      <c r="I92" s="23" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="J92" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L92" s="39" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="14" t="inlineStr">
-        <is>
-          <t>Jhoan Roa</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>@jhoan.roa</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Micro/Nano (&lt;1M)</t>
-        </is>
-      </c>
-      <c r="F93" s="37" t="n">
-        <v>946600</v>
-      </c>
-      <c r="G93" s="18" t="n">
-        <v>110.5</v>
-      </c>
-      <c r="H93" s="19" t="n">
-        <v>0.1292117647058824</v>
-      </c>
-      <c r="I93" s="18" t="n">
-        <v>116.7</v>
-      </c>
-      <c r="J93" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K93" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="B94" s="22" t="inlineStr">
-        <is>
-          <t>Kitty catKucing</t>
-        </is>
-      </c>
-      <c r="C94" s="39" t="inlineStr">
-        <is>
-          <t>@cat_kitty66</t>
-        </is>
-      </c>
-      <c r="D94" s="39" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E94" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F94" s="40" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="G94" s="23" t="n">
-        <v>108.1</v>
-      </c>
-      <c r="H94" s="24" t="n">
-        <v>0.1432960222016651</v>
-      </c>
-      <c r="I94" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="J94" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K94" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L94" s="39" t="inlineStr">
-        <is>
-          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="B95" s="14" t="inlineStr">
-        <is>
-          <t>Dilkash Dhany Ramn</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>@tizilwa</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F95" s="37" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="G95" s="18" t="n">
-        <v>102</v>
-      </c>
-      <c r="H95" s="19" t="n">
-        <v>0.08027450980392156</v>
-      </c>
-      <c r="I95" s="18" t="n">
-        <v>78.5</v>
-      </c>
-      <c r="J95" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="B96" s="22" t="inlineStr">
-        <is>
-          <t>Khaleesi</t>
-        </is>
-      </c>
-      <c r="C96" s="39" t="inlineStr">
-        <is>
-          <t>@thekhaleesicat</t>
-        </is>
-      </c>
-      <c r="D96" s="39" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E96" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F96" s="40" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="G96" s="23" t="n">
-        <v>100.6</v>
-      </c>
-      <c r="H96" s="24" t="n">
-        <v>0.08418290258449304</v>
-      </c>
-      <c r="I96" s="23" t="n">
-        <v>91.5</v>
-      </c>
-      <c r="J96" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L96" s="39" t="inlineStr">
-        <is>
-          <t>Engagement Émotionnel &amp; Fort Taux de Partage</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>Bandit the Raccoon</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>@banditthecoon</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Animaux &amp; Pets</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F97" s="37" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="G97" s="18" t="n">
-        <v>98.5</v>
-      </c>
-      <c r="H97" s="19" t="n">
-        <v>0.1922903553299492</v>
-      </c>
-      <c r="I97" s="18" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="J97" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K97" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>★ Pépite Virale (Recommandation Forte : Meilleur ROI)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="B98" s="22" t="inlineStr">
-        <is>
-          <t>Celiajunguito</t>
-        </is>
-      </c>
-      <c r="C98" s="39" t="inlineStr">
-        <is>
-          <t>@celiajunguito1</t>
-        </is>
-      </c>
-      <c r="D98" s="39" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E98" s="39" t="inlineStr">
-        <is>
-          <t>Micro/Nano (&lt;1M)</t>
-        </is>
-      </c>
-      <c r="F98" s="40" t="n">
-        <v>398400</v>
-      </c>
-      <c r="G98" s="23" t="n">
-        <v>97.2</v>
-      </c>
-      <c r="H98" s="24" t="n">
-        <v>0.07933230452674897</v>
-      </c>
-      <c r="I98" s="23" t="n">
-        <v>244</v>
-      </c>
-      <c r="J98" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K98" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L98" s="39" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="14" t="inlineStr">
-        <is>
-          <t>DADDY MING</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>@daddyming</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Famille &amp; Couple</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F99" s="37" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="G99" s="18" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="H99" s="19" t="n">
-        <v>0.09987074829931973</v>
-      </c>
-      <c r="I99" s="18" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J99" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K99" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="22" t="inlineStr">
-        <is>
-          <t>Kirya Kolesnikov</t>
-        </is>
-      </c>
-      <c r="C100" s="39" t="inlineStr">
-        <is>
-          <t>@thekiryalife</t>
-        </is>
-      </c>
-      <c r="D100" s="39" t="inlineStr">
-        <is>
-          <t>Talents &amp; Créativité</t>
-        </is>
-      </c>
-      <c r="E100" s="39" t="inlineStr">
-        <is>
-          <t>Mega (5M+)</t>
-        </is>
-      </c>
-      <c r="F100" s="40" t="n">
-        <v>33200000</v>
-      </c>
-      <c r="G100" s="23" t="n">
-        <v>82.3</v>
-      </c>
-      <c r="H100" s="24" t="n">
-        <v>0.0865820170109356</v>
-      </c>
-      <c r="I100" s="23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J100" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K100" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L100" s="39" t="inlineStr">
-        <is>
-          <t>Notoriété de Masse / Caution Institutionnelle</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="14" t="inlineStr">
-        <is>
-          <t>lastMinute_21</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>@lastminute_21</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Talents &amp; Créativité</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F101" s="37" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="G101" s="18" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="H101" s="19" t="n">
-        <v>0.09057803526448364</v>
-      </c>
-      <c r="I101" s="18" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="J101" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="22" t="inlineStr">
-        <is>
-          <t>Charlie</t>
-        </is>
-      </c>
-      <c r="C102" s="39" t="inlineStr">
-        <is>
-          <t>@charliethechipmunk</t>
-        </is>
-      </c>
-      <c r="D102" s="39" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E102" s="39" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F102" s="40" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="G102" s="23" t="n">
-        <v>77</v>
-      </c>
-      <c r="H102" s="24" t="n">
-        <v>0.1064285714285714</v>
-      </c>
-      <c r="I102" s="23" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="J102" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K102" s="41" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L102" s="39" t="inlineStr">
-        <is>
-          <t>Activation Thématique / Cœur de Cible</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="B103" s="14" t="inlineStr">
-        <is>
-          <t>crinka</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>@crinka11</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Humour &amp; Sketch</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Mid/Macro (1M-5M)</t>
-        </is>
-      </c>
-      <c r="F103" s="37" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="G103" s="18" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="H103" s="19" t="n">
-        <v>0.2087255434782609</v>
-      </c>
-      <c r="I103" s="18" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="J103" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K103" s="38" t="inlineStr">
-        <is>
-          <t>ER=(L+C+S)/V | Mult=V/Foll</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>★ Pépite Virale (Recommandation Forte : Meilleur ROI)</t>
         </is>
       </c>
     </row>
@@ -2972,14 +2314,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="42" t="inlineStr">
+      <c r="B2" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">  MATRICE STRATÉGIQUE D'AIDE À LA DÉCISION (STYLE BCG / GARTNER MAGIC QUADRANT)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="43" t="inlineStr">
+      <c r="B3" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">  Arbitrage Taux d'Engagement (%) vs Taille d'Audience | Taille des Bulles = Volume de Vues Cumulées</t>
         </is>
@@ -2993,135 +2335,135 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="28" t="inlineStr">
+      <c r="B34" s="35" t="inlineStr">
         <is>
           <t>Quadrant Stratégique</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="35" t="inlineStr">
         <is>
           <t>Profil Créateur</t>
         </is>
       </c>
-      <c r="D34" s="28" t="inlineStr">
+      <c r="D34" s="35" t="inlineStr">
         <is>
           <t>Seuils Data</t>
         </is>
       </c>
-      <c r="E34" s="28" t="inlineStr">
+      <c r="E34" s="35" t="inlineStr">
         <is>
           <t>Avantage Concurrentiel</t>
         </is>
       </c>
-      <c r="F34" s="28" t="inlineStr">
+      <c r="F34" s="35" t="inlineStr">
         <is>
           <t>Règle d'Allocation Budgétaire</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="36" t="inlineStr">
         <is>
           <t>QUADRANT 1 : Pépites Virales (Top-Left)</t>
         </is>
       </c>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>Micro/Nano créateurs hyper-actifs</t>
         </is>
       </c>
-      <c r="D35" s="31" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Followers &lt; 1M &amp; ER &gt; 15%</t>
         </is>
       </c>
-      <c r="E35" s="30" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr">
         <is>
           <t>Multiplicateur viral médian de 106,9x, coût d'activation très faible</t>
         </is>
       </c>
-      <c r="F35" s="32" t="inlineStr">
+      <c r="F35" s="39" t="inlineStr">
         <is>
           <t>Allouer 50% du budget influence pour maximiser le ROI</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="33" t="inlineStr">
+      <c r="B36" s="40" t="inlineStr">
         <is>
           <t>QUADRANT 2 : Stars d'Engagement (Top-Right)</t>
         </is>
       </c>
-      <c r="C36" s="30" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>Créateurs établis très engageants</t>
         </is>
       </c>
-      <c r="D36" s="31" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>Followers &gt; 1M &amp; ER &gt; 15%</t>
         </is>
       </c>
-      <c r="E36" s="30" t="inlineStr">
+      <c r="E36" s="37" t="inlineStr">
         <is>
           <t>Double force : forte communauté et audience captive fidèle</t>
         </is>
       </c>
-      <c r="F36" s="32" t="inlineStr">
+      <c r="F36" s="39" t="inlineStr">
         <is>
           <t>Allouer 20% du budget pour sécuriser des temps forts de campagne</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="34" t="inlineStr">
+      <c r="B37" s="41" t="inlineStr">
         <is>
           <t>QUADRANT 3 : Notoriété de Masse (Bottom-Right)</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="37" t="inlineStr">
         <is>
           <t>Mega stars et célébrités TikTok</t>
         </is>
       </c>
-      <c r="D37" s="31" t="inlineStr">
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Followers &gt; 5M &amp; ER &lt; 15%</t>
         </is>
       </c>
-      <c r="E37" s="30" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr">
         <is>
           <t>Volume de portée brute massif, forte légitimité institutionnelle</t>
         </is>
       </c>
-      <c r="F37" s="32" t="inlineStr">
+      <c r="F37" s="39" t="inlineStr">
         <is>
           <t>Allouer 30% du budget maximum (limiter à 1 ou 2 profils phares)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="42" t="inlineStr">
         <is>
           <t>QUADRANT 4 : Profils Émergents (Bottom-Left)</t>
         </is>
       </c>
-      <c r="C38" s="30" t="inlineStr">
+      <c r="C38" s="37" t="inlineStr">
         <is>
           <t>Créateurs en phase de test</t>
         </is>
       </c>
-      <c r="D38" s="31" t="inlineStr">
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>Followers &lt; 1M &amp; ER &lt; 15%</t>
         </is>
       </c>
-      <c r="E38" s="30" t="inlineStr">
+      <c r="E38" s="37" t="inlineStr">
         <is>
           <t>Faible coût, vivier d'expérimentation créative</t>
         </is>
       </c>
-      <c r="F38" s="32" t="inlineStr">
+      <c r="F38" s="39" t="inlineStr">
         <is>
           <t>Enveloppe de test &amp; learn (micro-dotations de produits)</t>
         </is>
@@ -3158,14 +2500,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="44" t="inlineStr">
+      <c r="B2" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">  DÉCOMPOSITION FACTORIELLE : CE QUE LE CRÉATEUR CONTRÔLE vs SUBIT</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
         <is>
           <t xml:space="preserve">  Tableaux de bord d'analyse de sensibilité : Durée, Audio, Taille d'Audience et Facteurs Neutres</t>
         </is>
@@ -3324,42 +2666,42 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="46" t="inlineStr">
+      <c r="B34" s="45" t="inlineStr">
         <is>
           <t>Type d'Audio</t>
         </is>
       </c>
-      <c r="C34" s="46" t="inlineStr">
+      <c r="C34" s="45" t="inlineStr">
         <is>
           <t>Nb Vidéos</t>
         </is>
       </c>
-      <c r="D34" s="46" t="inlineStr">
+      <c r="D34" s="45" t="inlineStr">
         <is>
           <t>Part (%)</t>
         </is>
       </c>
-      <c r="E34" s="46" t="inlineStr">
+      <c r="E34" s="45" t="inlineStr">
         <is>
           <t>Vues Moyennes (M)</t>
         </is>
       </c>
-      <c r="F34" s="46" t="inlineStr">
+      <c r="F34" s="45" t="inlineStr">
         <is>
           <t>Vues Médianes (M)</t>
         </is>
       </c>
-      <c r="G34" s="46" t="inlineStr">
+      <c r="G34" s="45" t="inlineStr">
         <is>
           <t>Taux Engagement Moyen (%)</t>
         </is>
       </c>
-      <c r="H34" s="46" t="inlineStr">
+      <c r="H34" s="45" t="inlineStr">
         <is>
           <t>Méthode de Calcul</t>
         </is>
       </c>
-      <c r="I34" s="46" t="inlineStr">
+      <c r="I34" s="45" t="inlineStr">
         <is>
           <t>Verdict Stratégique</t>
         </is>
@@ -3437,32 +2779,32 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="47" t="inlineStr">
+      <c r="B41" s="46" t="inlineStr">
         <is>
           <t>Facteur Écarté</t>
         </is>
       </c>
-      <c r="C41" s="47" t="inlineStr">
+      <c r="C41" s="46" t="inlineStr">
         <is>
           <t>Modalité Analysée A</t>
         </is>
       </c>
-      <c r="D41" s="47" t="inlineStr">
+      <c r="D41" s="46" t="inlineStr">
         <is>
           <t>Modalité Analysée B</t>
         </is>
       </c>
-      <c r="E41" s="47" t="inlineStr">
+      <c r="E41" s="46" t="inlineStr">
         <is>
           <t>Résultat Quantifié</t>
         </is>
       </c>
-      <c r="F41" s="47" t="inlineStr">
+      <c r="F41" s="46" t="inlineStr">
         <is>
           <t>Méthode / Test Statistique</t>
         </is>
       </c>
-      <c r="G41" s="47" t="inlineStr">
+      <c r="G41" s="46" t="inlineStr">
         <is>
           <t>Implication Décisionnelle pour le Client</t>
         </is>
@@ -3474,17 +2816,17 @@
           <t>Badge Certifié (Verified)</t>
         </is>
       </c>
-      <c r="C42" s="48" t="inlineStr">
+      <c r="C42" s="47" t="inlineStr">
         <is>
           <t>Avec Badge (41%) : 65,8 M vues moy.</t>
         </is>
       </c>
-      <c r="D42" s="48" t="inlineStr">
+      <c r="D42" s="47" t="inlineStr">
         <is>
           <t>Sans Badge (59%) : 70,2 M vues moy.</t>
         </is>
       </c>
-      <c r="E42" s="48" t="inlineStr">
+      <c r="E42" s="47" t="inlineStr">
         <is>
           <t>Aucune prime statistique de vues ni d'engagement (ER 15,5% vs 16,8%).</t>
         </is>
@@ -3538,17 +2880,17 @@
           <t>Historique de Vidéos du Compte</t>
         </is>
       </c>
-      <c r="C44" s="48" t="inlineStr">
+      <c r="C44" s="47" t="inlineStr">
         <is>
           <t>Moins de 100 vidéos : 68,4 M vues moy.</t>
         </is>
       </c>
-      <c r="D44" s="48" t="inlineStr">
+      <c r="D44" s="47" t="inlineStr">
         <is>
           <t>Plus de 500 vidéos : 69,1 M vues moy.</t>
         </is>
       </c>
-      <c r="E44" s="48" t="inlineStr">
+      <c r="E44" s="47" t="inlineStr">
         <is>
           <t>Corrélation quasi-nulle (r = +0.08 avec les vues).</t>
         </is>
@@ -3598,14 +2940,14 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="48" t="inlineStr">
         <is>
           <t xml:space="preserve">  SIMULATEUR BUDGÉTAIRE &amp; PROJECTIONS DE PERFORMANCE (CAMPAGNE B2C)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="49" t="inlineStr">
         <is>
           <t xml:space="preserve">  Modélisation financière sur une enveloppe type de 100 000 € : Comparatif Scénario Classique vs Recommandation Data-Driven</t>
         </is>
@@ -3641,7 +2983,7 @@
       <c r="L5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>100 000 €</t>
         </is>
@@ -3706,256 +3048,256 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="52" t="inlineStr">
+      <c r="B11" s="51" t="inlineStr">
         <is>
           <t>Indicateur Clé</t>
         </is>
       </c>
-      <c r="C11" s="52" t="inlineStr">
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>Scénario A : Approche Classique (100% Mega)</t>
         </is>
       </c>
-      <c r="D11" s="52" t="inlineStr">
+      <c r="D11" s="51" t="inlineStr">
         <is>
           <t>Scénario B : Approche Data-Driven (70% Micro/Mid + 30% Mega)</t>
         </is>
       </c>
-      <c r="E11" s="52" t="inlineStr">
+      <c r="E11" s="51" t="inlineStr">
         <is>
           <t>Différentiel Performance</t>
         </is>
       </c>
-      <c r="F11" s="52" t="inlineStr">
+      <c r="F11" s="51" t="inlineStr">
         <is>
           <t>Formule / Méthode de Calcul Utilisée</t>
         </is>
       </c>
-      <c r="G11" s="52" t="inlineStr">
+      <c r="G11" s="51" t="inlineStr">
         <is>
           <t>Impact Business pour la Marque B2C</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Nombre de Créateurs Activés</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>2 créateurs Mega</t>
         </is>
       </c>
-      <c r="D12" s="53" t="inlineStr">
+      <c r="D12" s="52" t="inlineStr">
         <is>
           <t>14 créateurs (11 Micro/Mid + 3 Mega)</t>
         </is>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="40" t="inlineStr">
         <is>
           <t>+600% de partenaires</t>
         </is>
       </c>
-      <c r="F12" s="31" t="inlineStr">
+      <c r="F12" s="38" t="inlineStr">
         <is>
           <t>Somme des profils sélectionnés</t>
         </is>
       </c>
-      <c r="G12" s="30" t="inlineStr">
+      <c r="G12" s="37" t="inlineStr">
         <is>
           <t>Diversification maximale du risque algorithmique</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>Budget Consacré</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>100 000 € (2 x 50k€)</t>
         </is>
       </c>
-      <c r="D13" s="53" t="inlineStr">
+      <c r="D13" s="52" t="inlineStr">
         <is>
           <t>100 000 € (70k€ Micro/Mid + 30k€ Mega)</t>
         </is>
       </c>
-      <c r="E13" s="33" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>Enveloppe identique</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
         <is>
           <t>Budget fixe alloué par la marque</t>
         </is>
       </c>
-      <c r="G13" s="30" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>Optimisation de l'allocation sans surcoût</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>Vues Totales Estimées</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="37" t="inlineStr">
         <is>
           <t>55,2 M de vues</t>
         </is>
       </c>
-      <c r="D14" s="53" t="inlineStr">
+      <c r="D14" s="52" t="inlineStr">
         <is>
           <t>118,5 M de vues</t>
         </is>
       </c>
-      <c r="E14" s="33" t="inlineStr">
+      <c r="E14" s="40" t="inlineStr">
         <is>
           <t>+114% de portée (+63,3M)</t>
         </is>
       </c>
-      <c r="F14" s="31" t="inlineStr">
+      <c r="F14" s="38" t="inlineStr">
         <is>
           <t>Somme(Nb_créateurs * Vues_Moyennes)</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G14" s="37" t="inlineStr">
         <is>
           <t>Audience doublée grâce au sur-rendement des micro-comptes</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>Taux d'Engagement Projeté</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>14,2 % (Interactions / Vues)</t>
         </is>
       </c>
-      <c r="D15" s="53" t="inlineStr">
+      <c r="D15" s="52" t="inlineStr">
         <is>
           <t>18,6 % (Interactions / Vues)</t>
         </is>
       </c>
-      <c r="E15" s="33" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>+4,4 pts d'engagement</t>
         </is>
       </c>
-      <c r="F15" s="31" t="inlineStr">
+      <c r="F15" s="38" t="inlineStr">
         <is>
           <t>Moyenne pondérée des ER par segment</t>
         </is>
       </c>
-      <c r="G15" s="30" t="inlineStr">
+      <c r="G15" s="37" t="inlineStr">
         <is>
           <t>Meilleure conversion organique et bouche-à-oreille</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>Total Interactions Projeté</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="37" t="inlineStr">
         <is>
           <t>7,84 Millions d'interactions</t>
         </is>
       </c>
-      <c r="D16" s="53" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>22,04 Millions d'interactions</t>
         </is>
       </c>
-      <c r="E16" s="33" t="inlineStr">
+      <c r="E16" s="40" t="inlineStr">
         <is>
           <t>+181% d'interactions</t>
         </is>
       </c>
-      <c r="F16" s="31" t="inlineStr">
+      <c r="F16" s="38" t="inlineStr">
         <is>
           <t>Vues Totales * Taux d'Engagement</t>
         </is>
       </c>
-      <c r="G16" s="30" t="inlineStr">
+      <c r="G16" s="37" t="inlineStr">
         <is>
           <t>Génération de contenu utilisateur et partage viral massif</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>Coût pour 1 000 Vues (CPM)</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="37" t="inlineStr">
         <is>
           <t>1,81 € par 1 000 vues</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>0,84 € par 1 000 vues</t>
         </is>
       </c>
-      <c r="E17" s="33" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>-54% sur le coût par vue</t>
         </is>
       </c>
-      <c r="F17" s="31" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
         <is>
           <t>CPM = (Budget / Vues Totales) * 1 000</t>
         </is>
       </c>
-      <c r="G17" s="30" t="inlineStr">
+      <c r="G17" s="37" t="inlineStr">
         <is>
           <t>Division par deux du coût d'acquisition de visibilité</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Vulnérabilité Algorithmique</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="37" t="inlineStr">
         <is>
           <t>Extrême (si 1 vidéo 'flop', 50% du budget est perdu)</t>
         </is>
       </c>
-      <c r="D18" s="53" t="inlineStr">
+      <c r="D18" s="52" t="inlineStr">
         <is>
           <t>Très faible (panier diversifié de 14 vidéos indépendantes)</t>
         </is>
       </c>
-      <c r="E18" s="33" t="inlineStr">
+      <c r="E18" s="40" t="inlineStr">
         <is>
           <t>Sécurité renforcée</t>
         </is>
       </c>
-      <c r="F18" s="31" t="inlineStr">
+      <c r="F18" s="38" t="inlineStr">
         <is>
           <t>Analyse de dispersion du risque</t>
         </is>
       </c>
-      <c r="G18" s="30" t="inlineStr">
+      <c r="G18" s="37" t="inlineStr">
         <is>
           <t>Garantie de résultat statistique pour la marque</t>
         </is>
@@ -3969,169 +3311,169 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="54" t="inlineStr">
+      <c r="B23" s="53" t="inlineStr">
         <is>
           <t>Segment Créateur</t>
         </is>
       </c>
-      <c r="C23" s="54" t="inlineStr">
+      <c r="C23" s="53" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="D23" s="54" t="inlineStr">
+      <c r="D23" s="53" t="inlineStr">
         <is>
           <t>Budget Moyen (€)</t>
         </is>
       </c>
-      <c r="E23" s="54" t="inlineStr">
+      <c r="E23" s="53" t="inlineStr">
         <is>
           <t>Budget Total Segment (€)</t>
         </is>
       </c>
-      <c r="F23" s="54" t="inlineStr">
+      <c r="F23" s="53" t="inlineStr">
         <is>
           <t>Vues Moyennes / Vidéo</t>
         </is>
       </c>
-      <c r="G23" s="54" t="inlineStr">
+      <c r="G23" s="53" t="inlineStr">
         <is>
           <t>Total Vues Segment (M)</t>
         </is>
       </c>
-      <c r="H23" s="54" t="inlineStr">
+      <c r="H23" s="53" t="inlineStr">
         <is>
           <t>Taux Engagement Moyen (%)</t>
         </is>
       </c>
-      <c r="I23" s="54" t="inlineStr">
+      <c r="I23" s="53" t="inlineStr">
         <is>
           <t>Formule Appliquée</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="32" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt; 1M followers)</t>
         </is>
       </c>
-      <c r="C24" s="55" t="n">
+      <c r="C24" s="54" t="n">
         <v>8</v>
       </c>
-      <c r="D24" s="56" t="n">
+      <c r="D24" s="55" t="n">
         <v>3500</v>
       </c>
-      <c r="E24" s="56" t="n">
+      <c r="E24" s="55" t="n">
         <v>28000</v>
       </c>
-      <c r="F24" s="56" t="n">
+      <c r="F24" s="55" t="n">
         <v>50800000</v>
       </c>
-      <c r="G24" s="57" t="n">
+      <c r="G24" s="56" t="n">
         <v>406.4</v>
       </c>
-      <c r="H24" s="58" t="n">
+      <c r="H24" s="57" t="n">
         <v>0.194</v>
       </c>
-      <c r="I24" s="31" t="inlineStr">
+      <c r="I24" s="38" t="inlineStr">
         <is>
           <t>Vues=(C24*F24)/1M | Budget=C24*D24</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Mid/Macro (1M - 5M followers)</t>
         </is>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C25" s="54" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="56" t="n">
+      <c r="D25" s="55" t="n">
         <v>8400</v>
       </c>
-      <c r="E25" s="56" t="n">
+      <c r="E25" s="55" t="n">
         <v>42000</v>
       </c>
-      <c r="F25" s="56" t="n">
+      <c r="F25" s="55" t="n">
         <v>82600000</v>
       </c>
-      <c r="G25" s="57" t="n">
+      <c r="G25" s="56" t="n">
         <v>413</v>
       </c>
-      <c r="H25" s="58" t="n">
+      <c r="H25" s="57" t="n">
         <v>0.148</v>
       </c>
-      <c r="I25" s="31" t="inlineStr">
+      <c r="I25" s="38" t="inlineStr">
         <is>
           <t>Vues=(C25*F25)/1M | Budget=C25*D25</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="32" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>Mega Influenceurs (5M+ followers)</t>
         </is>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C26" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="56" t="n">
+      <c r="D26" s="55" t="n">
         <v>30000</v>
       </c>
-      <c r="E26" s="56" t="n">
+      <c r="E26" s="55" t="n">
         <v>30000</v>
       </c>
-      <c r="F26" s="56" t="n">
+      <c r="F26" s="55" t="n">
         <v>68700000</v>
       </c>
-      <c r="G26" s="57" t="n">
+      <c r="G26" s="56" t="n">
         <v>68.7</v>
       </c>
-      <c r="H26" s="58" t="n">
+      <c r="H26" s="57" t="n">
         <v>0.152</v>
       </c>
-      <c r="I26" s="31" t="inlineStr">
+      <c r="I26" s="38" t="inlineStr">
         <is>
           <t>Vues=(C26*F26)/1M | Budget=C26*D26</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>TOTAL CAMPAGNE (SOMME &amp; MOYENNE)</t>
         </is>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="59">
         <f>SUM(C24:C26)</f>
         <v/>
       </c>
-      <c r="D27" s="61" t="inlineStr">
+      <c r="D27" s="60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E27" s="62">
+      <c r="E27" s="61">
         <f>SUM(E24:E26)</f>
         <v/>
       </c>
-      <c r="F27" s="61" t="inlineStr">
+      <c r="F27" s="60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G27" s="63">
+      <c r="G27" s="62">
         <f>SUM(G24:G26)</f>
         <v/>
       </c>
-      <c r="H27" s="64" t="n">
+      <c r="H27" s="63" t="n">
         <v>0.186</v>
       </c>
-      <c r="I27" s="65" t="inlineStr">
+      <c r="I27" s="64" t="inlineStr">
         <is>
           <t>Somme Budget &amp; Vues | ER pondéré</t>
         </is>
@@ -4186,14 +3528,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="66" t="inlineStr">
+      <c r="A1" s="65" t="inlineStr">
         <is>
           <t xml:space="preserve">  BASE DE DONNÉES PRÉPARÉE &amp; NETTOYÉE (100 OBSERVATIONS) — FORMAT CLIENT</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="67" t="inlineStr">
+      <c r="A2" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">  Conformité RGPD &amp; Règles Agence : Anonymisation des PII, suppression des identifiants techniques opaques et des données privées.</t>
         </is>
@@ -4201,82 +3543,82 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="68" t="inlineStr">
+      <c r="A4" s="67" t="inlineStr">
         <is>
           <t>N°</t>
         </is>
       </c>
-      <c r="B4" s="68" t="inlineStr">
+      <c r="B4" s="67" t="inlineStr">
         <is>
           <t>Handle_Createur</t>
         </is>
       </c>
-      <c r="C4" s="68" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>Nom_Affiche</t>
         </is>
       </c>
-      <c r="D4" s="68" t="inlineStr">
+      <c r="D4" s="67" t="inlineStr">
         <is>
           <t>Categorie</t>
         </is>
       </c>
-      <c r="E4" s="68" t="inlineStr">
+      <c r="E4" s="67" t="inlineStr">
         <is>
           <t>Segment_Followers</t>
         </is>
       </c>
-      <c r="F4" s="68" t="inlineStr">
+      <c r="F4" s="67" t="inlineStr">
         <is>
           <t>Abonnés</t>
         </is>
       </c>
-      <c r="G4" s="68" t="inlineStr">
+      <c r="G4" s="67" t="inlineStr">
         <is>
           <t>Duree_Sec</t>
         </is>
       </c>
-      <c r="H4" s="68" t="inlineStr">
+      <c r="H4" s="67" t="inlineStr">
         <is>
           <t>Vues</t>
         </is>
       </c>
-      <c r="I4" s="68" t="inlineStr">
+      <c r="I4" s="67" t="inlineStr">
         <is>
           <t>Likes</t>
         </is>
       </c>
-      <c r="J4" s="68" t="inlineStr">
+      <c r="J4" s="67" t="inlineStr">
         <is>
           <t>Commentaires</t>
         </is>
       </c>
-      <c r="K4" s="68" t="inlineStr">
+      <c r="K4" s="67" t="inlineStr">
         <is>
           <t>Partages</t>
         </is>
       </c>
-      <c r="L4" s="68" t="inlineStr">
+      <c r="L4" s="67" t="inlineStr">
         <is>
           <t>Total_Interactions (=I+J+K)</t>
         </is>
       </c>
-      <c r="M4" s="68" t="inlineStr">
+      <c r="M4" s="67" t="inlineStr">
         <is>
           <t>Taux_Engagement (=L/H)</t>
         </is>
       </c>
-      <c r="N4" s="68" t="inlineStr">
+      <c r="N4" s="67" t="inlineStr">
         <is>
           <t>Multiplicateur_Viral (=H/F)</t>
         </is>
       </c>
-      <c r="O4" s="68" t="inlineStr">
+      <c r="O4" s="67" t="inlineStr">
         <is>
           <t>Audio_Original</t>
         </is>
       </c>
-      <c r="P4" s="68" t="inlineStr">
+      <c r="P4" s="67" t="inlineStr">
         <is>
           <t>Badge_Certifie</t>
         </is>
@@ -4306,25 +3648,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="28" t="n">
         <v>3100000</v>
       </c>
       <c r="G5" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="H5" s="37" t="n">
+      <c r="H5" s="28" t="n">
         <v>280900000</v>
       </c>
-      <c r="I5" s="37" t="n">
+      <c r="I5" s="28" t="n">
         <v>35600000</v>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="28" t="n">
         <v>475900</v>
       </c>
-      <c r="K5" s="37" t="n">
+      <c r="K5" s="28" t="n">
         <v>2700000</v>
       </c>
-      <c r="L5" s="37">
+      <c r="L5" s="28">
         <f>I5+J5+K5</f>
         <v/>
       </c>
@@ -4351,45 +3693,45 @@
       <c r="A6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>@funnyvids2k21</t>
         </is>
       </c>
-      <c r="C6" s="39" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>Funny Vids 2k21</t>
         </is>
       </c>
-      <c r="D6" s="39" t="inlineStr">
+      <c r="D6" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E6" s="39" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="31" t="n">
         <v>4200000</v>
       </c>
       <c r="G6" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="H6" s="40" t="n">
+      <c r="H6" s="31" t="n">
         <v>197700000</v>
       </c>
-      <c r="I6" s="40" t="n">
+      <c r="I6" s="31" t="n">
         <v>18800000</v>
       </c>
-      <c r="J6" s="40" t="n">
+      <c r="J6" s="31" t="n">
         <v>236500</v>
       </c>
-      <c r="K6" s="40" t="n">
+      <c r="K6" s="31" t="n">
         <v>1200000</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6" s="31">
         <f>I6+J6+K6</f>
         <v/>
       </c>
@@ -4436,25 +3778,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F7" s="37" t="n">
+      <c r="F7" s="28" t="n">
         <v>7900000</v>
       </c>
       <c r="G7" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="H7" s="37" t="n">
+      <c r="H7" s="28" t="n">
         <v>144300000</v>
       </c>
-      <c r="I7" s="37" t="n">
+      <c r="I7" s="28" t="n">
         <v>18500000</v>
       </c>
-      <c r="J7" s="37" t="n">
+      <c r="J7" s="28" t="n">
         <v>222000</v>
       </c>
-      <c r="K7" s="37" t="n">
+      <c r="K7" s="28" t="n">
         <v>421400</v>
       </c>
-      <c r="L7" s="37">
+      <c r="L7" s="28">
         <f>I7+J7+K7</f>
         <v/>
       </c>
@@ -4481,45 +3823,45 @@
       <c r="A8" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>@banditthecoon</t>
         </is>
       </c>
-      <c r="C8" s="39" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>Bandit the Raccoon</t>
         </is>
       </c>
-      <c r="D8" s="39" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E8" s="39" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="31" t="n">
         <v>1400000</v>
       </c>
       <c r="G8" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H8" s="40" t="n">
+      <c r="H8" s="31" t="n">
         <v>98500000</v>
       </c>
-      <c r="I8" s="40" t="n">
+      <c r="I8" s="31" t="n">
         <v>18400000</v>
       </c>
-      <c r="J8" s="40" t="n">
+      <c r="J8" s="31" t="n">
         <v>157000</v>
       </c>
-      <c r="K8" s="40" t="n">
+      <c r="K8" s="31" t="n">
         <v>383600</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L8" s="31">
         <f>I8+J8+K8</f>
         <v/>
       </c>
@@ -4566,25 +3908,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F9" s="37" t="n">
+      <c r="F9" s="28" t="n">
         <v>27400000</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="H9" s="37" t="n">
+      <c r="H9" s="28" t="n">
         <v>141800000</v>
       </c>
-      <c r="I9" s="37" t="n">
+      <c r="I9" s="28" t="n">
         <v>16000000</v>
       </c>
-      <c r="J9" s="37" t="n">
+      <c r="J9" s="28" t="n">
         <v>163800</v>
       </c>
-      <c r="K9" s="37" t="n">
+      <c r="K9" s="28" t="n">
         <v>152600</v>
       </c>
-      <c r="L9" s="37">
+      <c r="L9" s="28">
         <f>I9+J9+K9</f>
         <v/>
       </c>
@@ -4611,45 +3953,45 @@
       <c r="A10" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>@crinka11</t>
         </is>
       </c>
-      <c r="C10" s="39" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>crinka</t>
         </is>
       </c>
-      <c r="D10" s="39" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E10" s="39" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="31" t="n">
         <v>1300000</v>
       </c>
       <c r="G10" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="H10" s="40" t="n">
+      <c r="H10" s="31" t="n">
         <v>73600000</v>
       </c>
-      <c r="I10" s="40" t="n">
+      <c r="I10" s="31" t="n">
         <v>15000000</v>
       </c>
-      <c r="J10" s="40" t="n">
+      <c r="J10" s="31" t="n">
         <v>164900</v>
       </c>
-      <c r="K10" s="40" t="n">
+      <c r="K10" s="31" t="n">
         <v>197300</v>
       </c>
-      <c r="L10" s="40">
+      <c r="L10" s="31">
         <f>I10+J10+K10</f>
         <v/>
       </c>
@@ -4696,25 +4038,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F11" s="37" t="n">
+      <c r="F11" s="28" t="n">
         <v>946600</v>
       </c>
       <c r="G11" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="H11" s="37" t="n">
+      <c r="H11" s="28" t="n">
         <v>110500000</v>
       </c>
-      <c r="I11" s="37" t="n">
+      <c r="I11" s="28" t="n">
         <v>14100000</v>
       </c>
-      <c r="J11" s="37" t="n">
+      <c r="J11" s="28" t="n">
         <v>49200</v>
       </c>
-      <c r="K11" s="37" t="n">
+      <c r="K11" s="28" t="n">
         <v>128700</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="28">
         <f>I11+J11+K11</f>
         <v/>
       </c>
@@ -4741,45 +4083,45 @@
       <c r="A12" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>@funnyvids2k21</t>
         </is>
       </c>
-      <c r="C12" s="39" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>Funny Vids 2k21</t>
         </is>
       </c>
-      <c r="D12" s="39" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E12" s="39" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="31" t="n">
         <v>4200000</v>
       </c>
       <c r="G12" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="40" t="n">
+      <c r="H12" s="31" t="n">
         <v>112400000</v>
       </c>
-      <c r="I12" s="40" t="n">
+      <c r="I12" s="31" t="n">
         <v>14100000</v>
       </c>
-      <c r="J12" s="40" t="n">
+      <c r="J12" s="31" t="n">
         <v>180200</v>
       </c>
-      <c r="K12" s="40" t="n">
+      <c r="K12" s="31" t="n">
         <v>601600</v>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="31">
         <f>I12+J12+K12</f>
         <v/>
       </c>
@@ -4826,25 +4168,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F13" s="37" t="n">
+      <c r="F13" s="28" t="n">
         <v>2700000</v>
       </c>
       <c r="G13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H13" s="37" t="n">
+      <c r="H13" s="28" t="n">
         <v>108100000</v>
       </c>
-      <c r="I13" s="37" t="n">
+      <c r="I13" s="28" t="n">
         <v>14000000</v>
       </c>
-      <c r="J13" s="37" t="n">
+      <c r="J13" s="28" t="n">
         <v>190300</v>
       </c>
-      <c r="K13" s="37" t="n">
+      <c r="K13" s="28" t="n">
         <v>1300000</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="28">
         <f>I13+J13+K13</f>
         <v/>
       </c>
@@ -4871,45 +4213,45 @@
       <c r="A14" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>@ox_zung</t>
         </is>
       </c>
-      <c r="C14" s="39" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>원정맨 WonJeong</t>
         </is>
       </c>
-      <c r="D14" s="39" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E14" s="39" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="31" t="n">
         <v>27400000</v>
       </c>
       <c r="G14" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="H14" s="40" t="n">
+      <c r="H14" s="31" t="n">
         <v>154900000</v>
       </c>
-      <c r="I14" s="40" t="n">
+      <c r="I14" s="31" t="n">
         <v>13800000</v>
       </c>
-      <c r="J14" s="40" t="n">
+      <c r="J14" s="31" t="n">
         <v>76100</v>
       </c>
-      <c r="K14" s="40" t="n">
+      <c r="K14" s="31" t="n">
         <v>60100</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="31">
         <f>I14+J14+K14</f>
         <v/>
       </c>
@@ -4956,25 +4298,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F15" s="37" t="n">
+      <c r="F15" s="28" t="n">
         <v>168400</v>
       </c>
       <c r="G15" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="H15" s="37" t="n">
+      <c r="H15" s="28" t="n">
         <v>59400000</v>
       </c>
-      <c r="I15" s="37" t="n">
+      <c r="I15" s="28" t="n">
         <v>12500000</v>
       </c>
-      <c r="J15" s="37" t="n">
+      <c r="J15" s="28" t="n">
         <v>364600</v>
       </c>
-      <c r="K15" s="37" t="n">
+      <c r="K15" s="28" t="n">
         <v>1000000</v>
       </c>
-      <c r="L15" s="37">
+      <c r="L15" s="28">
         <f>I15+J15+K15</f>
         <v/>
       </c>
@@ -5001,45 +4343,45 @@
       <c r="A16" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>@samuelgrubbs</t>
         </is>
       </c>
-      <c r="C16" s="39" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>Samuel Grubbs</t>
         </is>
       </c>
-      <c r="D16" s="39" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E16" s="39" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="31" t="n">
         <v>7900000</v>
       </c>
       <c r="G16" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="H16" s="40" t="n">
+      <c r="H16" s="31" t="n">
         <v>126600000</v>
       </c>
-      <c r="I16" s="40" t="n">
+      <c r="I16" s="31" t="n">
         <v>12000000</v>
       </c>
-      <c r="J16" s="40" t="n">
+      <c r="J16" s="31" t="n">
         <v>60100</v>
       </c>
-      <c r="K16" s="40" t="n">
+      <c r="K16" s="31" t="n">
         <v>701300</v>
       </c>
-      <c r="L16" s="40">
+      <c r="L16" s="31">
         <f>I16+J16+K16</f>
         <v/>
       </c>
@@ -5086,25 +4428,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F17" s="37" t="n">
+      <c r="F17" s="28" t="n">
         <v>2100000</v>
       </c>
       <c r="G17" s="20" t="n">
         <v>57</v>
       </c>
-      <c r="H17" s="37" t="n">
+      <c r="H17" s="28" t="n">
         <v>62400000</v>
       </c>
-      <c r="I17" s="37" t="n">
+      <c r="I17" s="28" t="n">
         <v>11900000</v>
       </c>
-      <c r="J17" s="37" t="n">
+      <c r="J17" s="28" t="n">
         <v>89600</v>
       </c>
-      <c r="K17" s="37" t="n">
+      <c r="K17" s="28" t="n">
         <v>203800</v>
       </c>
-      <c r="L17" s="37">
+      <c r="L17" s="28">
         <f>I17+J17+K17</f>
         <v/>
       </c>
@@ -5131,45 +4473,45 @@
       <c r="A18" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>@lexnotalexis</t>
         </is>
       </c>
-      <c r="C18" s="39" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>lex</t>
         </is>
       </c>
-      <c r="D18" s="39" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E18" s="39" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="31" t="n">
         <v>381700</v>
       </c>
       <c r="G18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="H18" s="40" t="n">
+      <c r="H18" s="31" t="n">
         <v>52600000</v>
       </c>
-      <c r="I18" s="40" t="n">
+      <c r="I18" s="31" t="n">
         <v>11400000</v>
       </c>
-      <c r="J18" s="40" t="n">
+      <c r="J18" s="31" t="n">
         <v>87300</v>
       </c>
-      <c r="K18" s="40" t="n">
+      <c r="K18" s="31" t="n">
         <v>237300</v>
       </c>
-      <c r="L18" s="40">
+      <c r="L18" s="31">
         <f>I18+J18+K18</f>
         <v/>
       </c>
@@ -5216,25 +4558,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F19" s="37" t="n">
+      <c r="F19" s="28" t="n">
         <v>3500000</v>
       </c>
       <c r="G19" s="20" t="n">
         <v>59</v>
       </c>
-      <c r="H19" s="37" t="n">
+      <c r="H19" s="28" t="n">
         <v>65900000</v>
       </c>
-      <c r="I19" s="37" t="n">
+      <c r="I19" s="28" t="n">
         <v>11200000</v>
       </c>
-      <c r="J19" s="37" t="n">
+      <c r="J19" s="28" t="n">
         <v>188300</v>
       </c>
-      <c r="K19" s="37" t="n">
+      <c r="K19" s="28" t="n">
         <v>728700</v>
       </c>
-      <c r="L19" s="37">
+      <c r="L19" s="28">
         <f>I19+J19+K19</f>
         <v/>
       </c>
@@ -5261,45 +4603,45 @@
       <c r="A20" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>@johnn_deer</t>
         </is>
       </c>
-      <c r="C20" s="39" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Thomas</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E20" s="39" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="31" t="n">
         <v>144200</v>
       </c>
       <c r="G20" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="40" t="n">
+      <c r="H20" s="31" t="n">
         <v>46100000</v>
       </c>
-      <c r="I20" s="40" t="n">
+      <c r="I20" s="31" t="n">
         <v>11200000</v>
       </c>
-      <c r="J20" s="40" t="n">
+      <c r="J20" s="31" t="n">
         <v>227900</v>
       </c>
-      <c r="K20" s="40" t="n">
+      <c r="K20" s="31" t="n">
         <v>390800</v>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="31">
         <f>I20+J20+K20</f>
         <v/>
       </c>
@@ -5346,25 +4688,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F21" s="37" t="n">
+      <c r="F21" s="28" t="n">
         <v>7900000</v>
       </c>
       <c r="G21" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="H21" s="37" t="n">
+      <c r="H21" s="28" t="n">
         <v>77000000</v>
       </c>
-      <c r="I21" s="37" t="n">
+      <c r="I21" s="28" t="n">
         <v>11000000</v>
       </c>
-      <c r="J21" s="37" t="n">
+      <c r="J21" s="28" t="n">
         <v>56300</v>
       </c>
-      <c r="K21" s="37" t="n">
+      <c r="K21" s="28" t="n">
         <v>194300</v>
       </c>
-      <c r="L21" s="37">
+      <c r="L21" s="28">
         <f>I21+J21+K21</f>
         <v/>
       </c>
@@ -5391,45 +4733,45 @@
       <c r="A22" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>@mercuri_88</t>
         </is>
       </c>
-      <c r="C22" s="39" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>Manuel Mercuri</t>
         </is>
       </c>
-      <c r="D22" s="39" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E22" s="39" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F22" s="40" t="n">
+      <c r="F22" s="31" t="n">
         <v>14500000</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H22" s="40" t="n">
+      <c r="H22" s="31" t="n">
         <v>75700000</v>
       </c>
-      <c r="I22" s="40" t="n">
+      <c r="I22" s="31" t="n">
         <v>10600000</v>
       </c>
-      <c r="J22" s="40" t="n">
+      <c r="J22" s="31" t="n">
         <v>111500</v>
       </c>
-      <c r="K22" s="40" t="n">
+      <c r="K22" s="31" t="n">
         <v>267700</v>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="31">
         <f>I22+J22+K22</f>
         <v/>
       </c>
@@ -5476,25 +4818,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="28" t="n">
         <v>5200000</v>
       </c>
       <c r="G23" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="H23" s="37" t="n">
+      <c r="H23" s="28" t="n">
         <v>52100000</v>
       </c>
-      <c r="I23" s="37" t="n">
+      <c r="I23" s="28" t="n">
         <v>10400000</v>
       </c>
-      <c r="J23" s="37" t="n">
+      <c r="J23" s="28" t="n">
         <v>30000</v>
       </c>
-      <c r="K23" s="37" t="n">
+      <c r="K23" s="28" t="n">
         <v>32000</v>
       </c>
-      <c r="L23" s="37">
+      <c r="L23" s="28">
         <f>I23+J23+K23</f>
         <v/>
       </c>
@@ -5521,45 +4863,45 @@
       <c r="A24" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>@cs99tv</t>
         </is>
       </c>
-      <c r="C24" s="39" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>CS99TV</t>
         </is>
       </c>
-      <c r="D24" s="39" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>Sports &amp; Gaming</t>
         </is>
       </c>
-      <c r="E24" s="39" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F24" s="40" t="n">
+      <c r="F24" s="31" t="n">
         <v>2300000</v>
       </c>
       <c r="G24" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="H24" s="40" t="n">
+      <c r="H24" s="31" t="n">
         <v>106200000</v>
       </c>
-      <c r="I24" s="40" t="n">
+      <c r="I24" s="31" t="n">
         <v>10400000</v>
       </c>
-      <c r="J24" s="40" t="n">
+      <c r="J24" s="31" t="n">
         <v>14000</v>
       </c>
-      <c r="K24" s="40" t="n">
+      <c r="K24" s="31" t="n">
         <v>19400</v>
       </c>
-      <c r="L24" s="40">
+      <c r="L24" s="31">
         <f>I24+J24+K24</f>
         <v/>
       </c>
@@ -5606,25 +4948,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F25" s="37" t="n">
+      <c r="F25" s="28" t="n">
         <v>547000</v>
       </c>
       <c r="G25" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="H25" s="37" t="n">
+      <c r="H25" s="28" t="n">
         <v>71200000</v>
       </c>
-      <c r="I25" s="37" t="n">
+      <c r="I25" s="28" t="n">
         <v>10300000</v>
       </c>
-      <c r="J25" s="37" t="n">
+      <c r="J25" s="28" t="n">
         <v>328100</v>
       </c>
-      <c r="K25" s="37" t="n">
+      <c r="K25" s="28" t="n">
         <v>655800</v>
       </c>
-      <c r="L25" s="37">
+      <c r="L25" s="28">
         <f>I25+J25+K25</f>
         <v/>
       </c>
@@ -5651,45 +4993,45 @@
       <c r="A26" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>@samuelgrubbs</t>
         </is>
       </c>
-      <c r="C26" s="39" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>Samuel Grubbs</t>
         </is>
       </c>
-      <c r="D26" s="39" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E26" s="39" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F26" s="40" t="n">
+      <c r="F26" s="31" t="n">
         <v>7900000</v>
       </c>
       <c r="G26" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="H26" s="40" t="n">
+      <c r="H26" s="31" t="n">
         <v>60300000</v>
       </c>
-      <c r="I26" s="40" t="n">
+      <c r="I26" s="31" t="n">
         <v>10300000</v>
       </c>
-      <c r="J26" s="40" t="n">
+      <c r="J26" s="31" t="n">
         <v>109800</v>
       </c>
-      <c r="K26" s="40" t="n">
+      <c r="K26" s="31" t="n">
         <v>186400</v>
       </c>
-      <c r="L26" s="40">
+      <c r="L26" s="31">
         <f>I26+J26+K26</f>
         <v/>
       </c>
@@ -5736,25 +5078,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F27" s="37" t="n">
+      <c r="F27" s="28" t="n">
         <v>1000000</v>
       </c>
       <c r="G27" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H27" s="37" t="n">
+      <c r="H27" s="28" t="n">
         <v>44200000</v>
       </c>
-      <c r="I27" s="37" t="n">
+      <c r="I27" s="28" t="n">
         <v>10200000</v>
       </c>
-      <c r="J27" s="37" t="n">
+      <c r="J27" s="28" t="n">
         <v>26500</v>
       </c>
-      <c r="K27" s="37" t="n">
+      <c r="K27" s="28" t="n">
         <v>27000</v>
       </c>
-      <c r="L27" s="37">
+      <c r="L27" s="28">
         <f>I27+J27+K27</f>
         <v/>
       </c>
@@ -5781,45 +5123,45 @@
       <c r="A28" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>@ibc_kid</t>
         </is>
       </c>
-      <c r="C28" s="39" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>𝕚𝕓𝕔_𝕜𝕚𝕕</t>
         </is>
       </c>
-      <c r="D28" s="39" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E28" s="39" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F28" s="40" t="n">
+      <c r="F28" s="31" t="n">
         <v>933700</v>
       </c>
       <c r="G28" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="40" t="n">
+      <c r="H28" s="31" t="n">
         <v>63700000</v>
       </c>
-      <c r="I28" s="40" t="n">
+      <c r="I28" s="31" t="n">
         <v>10100000</v>
       </c>
-      <c r="J28" s="40" t="n">
+      <c r="J28" s="31" t="n">
         <v>93500</v>
       </c>
-      <c r="K28" s="40" t="n">
+      <c r="K28" s="31" t="n">
         <v>277100</v>
       </c>
-      <c r="L28" s="40">
+      <c r="L28" s="31">
         <f>I28+J28+K28</f>
         <v/>
       </c>
@@ -5866,25 +5208,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F29" s="37" t="n">
+      <c r="F29" s="28" t="n">
         <v>9100000</v>
       </c>
       <c r="G29" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="H29" s="37" t="n">
+      <c r="H29" s="28" t="n">
         <v>112600000</v>
       </c>
-      <c r="I29" s="37" t="n">
+      <c r="I29" s="28" t="n">
         <v>10000000</v>
       </c>
-      <c r="J29" s="37" t="n">
+      <c r="J29" s="28" t="n">
         <v>14100</v>
       </c>
-      <c r="K29" s="37" t="n">
+      <c r="K29" s="28" t="n">
         <v>39600</v>
       </c>
-      <c r="L29" s="37">
+      <c r="L29" s="28">
         <f>I29+J29+K29</f>
         <v/>
       </c>
@@ -5911,45 +5253,45 @@
       <c r="A30" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>@ox_zung</t>
         </is>
       </c>
-      <c r="C30" s="39" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>원정맨 WonJeong</t>
         </is>
       </c>
-      <c r="D30" s="39" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E30" s="39" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F30" s="40" t="n">
+      <c r="F30" s="31" t="n">
         <v>27400000</v>
       </c>
       <c r="G30" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="H30" s="40" t="n">
+      <c r="H30" s="31" t="n">
         <v>54200000</v>
       </c>
-      <c r="I30" s="40" t="n">
+      <c r="I30" s="31" t="n">
         <v>10000000</v>
       </c>
-      <c r="J30" s="40" t="n">
+      <c r="J30" s="31" t="n">
         <v>94100</v>
       </c>
-      <c r="K30" s="40" t="n">
+      <c r="K30" s="31" t="n">
         <v>78600</v>
       </c>
-      <c r="L30" s="40">
+      <c r="L30" s="31">
         <f>I30+J30+K30</f>
         <v/>
       </c>
@@ -5996,25 +5338,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F31" s="37" t="n">
+      <c r="F31" s="28" t="n">
         <v>1800000</v>
       </c>
       <c r="G31" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="H31" s="37" t="n">
+      <c r="H31" s="28" t="n">
         <v>48300000</v>
       </c>
-      <c r="I31" s="37" t="n">
+      <c r="I31" s="28" t="n">
         <v>9900000</v>
       </c>
-      <c r="J31" s="37" t="n">
+      <c r="J31" s="28" t="n">
         <v>63100</v>
       </c>
-      <c r="K31" s="37" t="n">
+      <c r="K31" s="28" t="n">
         <v>312000</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="28">
         <f>I31+J31+K31</f>
         <v/>
       </c>
@@ -6041,45 +5383,45 @@
       <c r="A32" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>@bobbymoore44</t>
         </is>
       </c>
-      <c r="C32" s="39" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>Bobby Moore</t>
         </is>
       </c>
-      <c r="D32" s="39" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E32" s="39" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F32" s="40" t="n">
+      <c r="F32" s="31" t="n">
         <v>7900000</v>
       </c>
       <c r="G32" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="H32" s="40" t="n">
+      <c r="H32" s="31" t="n">
         <v>49600000</v>
       </c>
-      <c r="I32" s="40" t="n">
+      <c r="I32" s="31" t="n">
         <v>9900000</v>
       </c>
-      <c r="J32" s="40" t="n">
+      <c r="J32" s="31" t="n">
         <v>41200</v>
       </c>
-      <c r="K32" s="40" t="n">
+      <c r="K32" s="31" t="n">
         <v>536500</v>
       </c>
-      <c r="L32" s="40">
+      <c r="L32" s="31">
         <f>I32+J32+K32</f>
         <v/>
       </c>
@@ -6126,25 +5468,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F33" s="37" t="n">
+      <c r="F33" s="28" t="n">
         <v>6300000</v>
       </c>
       <c r="G33" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="H33" s="37" t="n">
+      <c r="H33" s="28" t="n">
         <v>55200000</v>
       </c>
-      <c r="I33" s="37" t="n">
+      <c r="I33" s="28" t="n">
         <v>9700000</v>
       </c>
-      <c r="J33" s="37" t="n">
+      <c r="J33" s="28" t="n">
         <v>99000</v>
       </c>
-      <c r="K33" s="37" t="n">
+      <c r="K33" s="28" t="n">
         <v>712400</v>
       </c>
-      <c r="L33" s="37">
+      <c r="L33" s="28">
         <f>I33+J33+K33</f>
         <v/>
       </c>
@@ -6171,45 +5513,45 @@
       <c r="A34" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>@onlee1momo</t>
         </is>
       </c>
-      <c r="C34" s="39" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>onlee1momo</t>
         </is>
       </c>
-      <c r="D34" s="39" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E34" s="39" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F34" s="40" t="n">
+      <c r="F34" s="31" t="n">
         <v>362600</v>
       </c>
       <c r="G34" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="H34" s="40" t="n">
+      <c r="H34" s="31" t="n">
         <v>66000000</v>
       </c>
-      <c r="I34" s="40" t="n">
+      <c r="I34" s="31" t="n">
         <v>9700000</v>
       </c>
-      <c r="J34" s="40" t="n">
+      <c r="J34" s="31" t="n">
         <v>541500</v>
       </c>
-      <c r="K34" s="40" t="n">
+      <c r="K34" s="31" t="n">
         <v>846900</v>
       </c>
-      <c r="L34" s="40">
+      <c r="L34" s="31">
         <f>I34+J34+K34</f>
         <v/>
       </c>
@@ -6256,25 +5598,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F35" s="37" t="n">
+      <c r="F35" s="28" t="n">
         <v>158600</v>
       </c>
       <c r="G35" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="H35" s="37" t="n">
+      <c r="H35" s="28" t="n">
         <v>42800000</v>
       </c>
-      <c r="I35" s="37" t="n">
+      <c r="I35" s="28" t="n">
         <v>9700000</v>
       </c>
-      <c r="J35" s="37" t="n">
+      <c r="J35" s="28" t="n">
         <v>48100</v>
       </c>
-      <c r="K35" s="37" t="n">
+      <c r="K35" s="28" t="n">
         <v>82700</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="28">
         <f>I35+J35+K35</f>
         <v/>
       </c>
@@ -6301,45 +5643,45 @@
       <c r="A36" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>@jordi.koalitic</t>
         </is>
       </c>
-      <c r="C36" s="39" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>Jordi.koalitic</t>
         </is>
       </c>
-      <c r="D36" s="39" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E36" s="39" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F36" s="40" t="n">
+      <c r="F36" s="31" t="n">
         <v>19700000</v>
       </c>
       <c r="G36" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="H36" s="40" t="n">
+      <c r="H36" s="31" t="n">
         <v>74400000</v>
       </c>
-      <c r="I36" s="40" t="n">
+      <c r="I36" s="31" t="n">
         <v>9500000</v>
       </c>
-      <c r="J36" s="40" t="n">
+      <c r="J36" s="31" t="n">
         <v>27600</v>
       </c>
-      <c r="K36" s="40" t="n">
+      <c r="K36" s="31" t="n">
         <v>103400</v>
       </c>
-      <c r="L36" s="40">
+      <c r="L36" s="31">
         <f>I36+J36+K36</f>
         <v/>
       </c>
@@ -6386,25 +5728,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F37" s="37" t="n">
+      <c r="F37" s="28" t="n">
         <v>18400000</v>
       </c>
       <c r="G37" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="H37" s="37" t="n">
+      <c r="H37" s="28" t="n">
         <v>42700000</v>
       </c>
-      <c r="I37" s="37" t="n">
+      <c r="I37" s="28" t="n">
         <v>9400000</v>
       </c>
-      <c r="J37" s="37" t="n">
+      <c r="J37" s="28" t="n">
         <v>88800</v>
       </c>
-      <c r="K37" s="37" t="n">
+      <c r="K37" s="28" t="n">
         <v>242200</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="28">
         <f>I37+J37+K37</f>
         <v/>
       </c>
@@ -6431,45 +5773,45 @@
       <c r="A38" s="25" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>@ludwig441</t>
         </is>
       </c>
-      <c r="C38" s="39" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>Chan</t>
         </is>
       </c>
-      <c r="D38" s="39" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E38" s="39" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F38" s="40" t="n">
+      <c r="F38" s="31" t="n">
         <v>614100</v>
       </c>
       <c r="G38" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="H38" s="40" t="n">
+      <c r="H38" s="31" t="n">
         <v>46300000</v>
       </c>
-      <c r="I38" s="40" t="n">
+      <c r="I38" s="31" t="n">
         <v>9300000</v>
       </c>
-      <c r="J38" s="40" t="n">
+      <c r="J38" s="31" t="n">
         <v>146200</v>
       </c>
-      <c r="K38" s="40" t="n">
+      <c r="K38" s="31" t="n">
         <v>210900</v>
       </c>
-      <c r="L38" s="40">
+      <c r="L38" s="31">
         <f>I38+J38+K38</f>
         <v/>
       </c>
@@ -6516,25 +5858,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F39" s="37" t="n">
+      <c r="F39" s="28" t="n">
         <v>346800</v>
       </c>
       <c r="G39" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="H39" s="37" t="n">
+      <c r="H39" s="28" t="n">
         <v>50900000</v>
       </c>
-      <c r="I39" s="37" t="n">
+      <c r="I39" s="28" t="n">
         <v>9300000</v>
       </c>
-      <c r="J39" s="37" t="n">
+      <c r="J39" s="28" t="n">
         <v>90000</v>
       </c>
-      <c r="K39" s="37" t="n">
+      <c r="K39" s="28" t="n">
         <v>89600</v>
       </c>
-      <c r="L39" s="37">
+      <c r="L39" s="28">
         <f>I39+J39+K39</f>
         <v/>
       </c>
@@ -6561,45 +5903,45 @@
       <c r="A40" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="39" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>@daquan</t>
         </is>
       </c>
-      <c r="C40" s="39" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>daquan</t>
         </is>
       </c>
-      <c r="D40" s="39" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E40" s="39" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F40" s="40" t="n">
+      <c r="F40" s="31" t="n">
         <v>8700000</v>
       </c>
       <c r="G40" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="H40" s="40" t="n">
+      <c r="H40" s="31" t="n">
         <v>51900000</v>
       </c>
-      <c r="I40" s="40" t="n">
+      <c r="I40" s="31" t="n">
         <v>9100000</v>
       </c>
-      <c r="J40" s="40" t="n">
+      <c r="J40" s="31" t="n">
         <v>71500</v>
       </c>
-      <c r="K40" s="40" t="n">
+      <c r="K40" s="31" t="n">
         <v>349700</v>
       </c>
-      <c r="L40" s="40">
+      <c r="L40" s="31">
         <f>I40+J40+K40</f>
         <v/>
       </c>
@@ -6646,25 +5988,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F41" s="37" t="n">
+      <c r="F41" s="28" t="n">
         <v>2300000</v>
       </c>
       <c r="G41" s="20" t="n">
         <v>59</v>
       </c>
-      <c r="H41" s="37" t="n">
+      <c r="H41" s="28" t="n">
         <v>45200000</v>
       </c>
-      <c r="I41" s="37" t="n">
+      <c r="I41" s="28" t="n">
         <v>9100000</v>
       </c>
-      <c r="J41" s="37" t="n">
+      <c r="J41" s="28" t="n">
         <v>46900</v>
       </c>
-      <c r="K41" s="37" t="n">
+      <c r="K41" s="28" t="n">
         <v>86100</v>
       </c>
-      <c r="L41" s="37">
+      <c r="L41" s="28">
         <f>I41+J41+K41</f>
         <v/>
       </c>
@@ -6691,45 +6033,45 @@
       <c r="A42" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="39" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>@ox_zung</t>
         </is>
       </c>
-      <c r="C42" s="39" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>원정맨 WonJeong</t>
         </is>
       </c>
-      <c r="D42" s="39" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E42" s="39" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F42" s="40" t="n">
+      <c r="F42" s="31" t="n">
         <v>27400000</v>
       </c>
       <c r="G42" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="H42" s="40" t="n">
+      <c r="H42" s="31" t="n">
         <v>85700000</v>
       </c>
-      <c r="I42" s="40" t="n">
+      <c r="I42" s="31" t="n">
         <v>9100000</v>
       </c>
-      <c r="J42" s="40" t="n">
+      <c r="J42" s="31" t="n">
         <v>47100</v>
       </c>
-      <c r="K42" s="40" t="n">
+      <c r="K42" s="31" t="n">
         <v>33900</v>
       </c>
-      <c r="L42" s="40">
+      <c r="L42" s="31">
         <f>I42+J42+K42</f>
         <v/>
       </c>
@@ -6776,25 +6118,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F43" s="37" t="n">
+      <c r="F43" s="28" t="n">
         <v>256100</v>
       </c>
       <c r="G43" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="H43" s="37" t="n">
+      <c r="H43" s="28" t="n">
         <v>48100000</v>
       </c>
-      <c r="I43" s="37" t="n">
+      <c r="I43" s="28" t="n">
         <v>9000000</v>
       </c>
-      <c r="J43" s="37" t="n">
+      <c r="J43" s="28" t="n">
         <v>110400</v>
       </c>
-      <c r="K43" s="37" t="n">
+      <c r="K43" s="28" t="n">
         <v>269700</v>
       </c>
-      <c r="L43" s="37">
+      <c r="L43" s="28">
         <f>I43+J43+K43</f>
         <v/>
       </c>
@@ -6821,45 +6163,45 @@
       <c r="A44" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>@iammarcohall</t>
         </is>
       </c>
-      <c r="C44" s="39" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>Marco Hall</t>
         </is>
       </c>
-      <c r="D44" s="39" t="inlineStr">
+      <c r="D44" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E44" s="39" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F44" s="40" t="n">
+      <c r="F44" s="31" t="n">
         <v>6500000</v>
       </c>
       <c r="G44" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="H44" s="40" t="n">
+      <c r="H44" s="31" t="n">
         <v>49400000</v>
       </c>
-      <c r="I44" s="40" t="n">
+      <c r="I44" s="31" t="n">
         <v>8900000</v>
       </c>
-      <c r="J44" s="40" t="n">
+      <c r="J44" s="31" t="n">
         <v>93800</v>
       </c>
-      <c r="K44" s="40" t="n">
+      <c r="K44" s="31" t="n">
         <v>253400</v>
       </c>
-      <c r="L44" s="40">
+      <c r="L44" s="31">
         <f>I44+J44+K44</f>
         <v/>
       </c>
@@ -6906,25 +6248,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F45" s="37" t="n">
+      <c r="F45" s="28" t="n">
         <v>7900000</v>
       </c>
       <c r="G45" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="H45" s="37" t="n">
+      <c r="H45" s="28" t="n">
         <v>61400000</v>
       </c>
-      <c r="I45" s="37" t="n">
+      <c r="I45" s="28" t="n">
         <v>8900000</v>
       </c>
-      <c r="J45" s="37" t="n">
+      <c r="J45" s="28" t="n">
         <v>107300</v>
       </c>
-      <c r="K45" s="37" t="n">
+      <c r="K45" s="28" t="n">
         <v>231100</v>
       </c>
-      <c r="L45" s="37">
+      <c r="L45" s="28">
         <f>I45+J45+K45</f>
         <v/>
       </c>
@@ -6951,45 +6293,45 @@
       <c r="A46" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>@mully</t>
         </is>
       </c>
-      <c r="C46" s="39" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>Mully</t>
         </is>
       </c>
-      <c r="D46" s="39" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E46" s="39" t="inlineStr">
+      <c r="E46" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F46" s="40" t="n">
+      <c r="F46" s="31" t="n">
         <v>10400000</v>
       </c>
       <c r="G46" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H46" s="40" t="n">
+      <c r="H46" s="31" t="n">
         <v>60700000</v>
       </c>
-      <c r="I46" s="40" t="n">
+      <c r="I46" s="31" t="n">
         <v>8800000</v>
       </c>
-      <c r="J46" s="40" t="n">
+      <c r="J46" s="31" t="n">
         <v>57000</v>
       </c>
-      <c r="K46" s="40" t="n">
+      <c r="K46" s="31" t="n">
         <v>514600</v>
       </c>
-      <c r="L46" s="40">
+      <c r="L46" s="31">
         <f>I46+J46+K46</f>
         <v/>
       </c>
@@ -7036,25 +6378,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F47" s="37" t="n">
+      <c r="F47" s="28" t="n">
         <v>2300000</v>
       </c>
       <c r="G47" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="H47" s="37" t="n">
+      <c r="H47" s="28" t="n">
         <v>43300000</v>
       </c>
-      <c r="I47" s="37" t="n">
+      <c r="I47" s="28" t="n">
         <v>8700000</v>
       </c>
-      <c r="J47" s="37" t="n">
+      <c r="J47" s="28" t="n">
         <v>80800</v>
       </c>
-      <c r="K47" s="37" t="n">
+      <c r="K47" s="28" t="n">
         <v>784100</v>
       </c>
-      <c r="L47" s="37">
+      <c r="L47" s="28">
         <f>I47+J47+K47</f>
         <v/>
       </c>
@@ -7081,45 +6423,45 @@
       <c r="A48" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>@samuelgrubbs</t>
         </is>
       </c>
-      <c r="C48" s="39" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>Samuel Grubbs</t>
         </is>
       </c>
-      <c r="D48" s="39" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E48" s="39" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F48" s="40" t="n">
+      <c r="F48" s="31" t="n">
         <v>7900000</v>
       </c>
       <c r="G48" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="H48" s="40" t="n">
+      <c r="H48" s="31" t="n">
         <v>49700000</v>
       </c>
-      <c r="I48" s="40" t="n">
+      <c r="I48" s="31" t="n">
         <v>8700000</v>
       </c>
-      <c r="J48" s="40" t="n">
+      <c r="J48" s="31" t="n">
         <v>143200</v>
       </c>
-      <c r="K48" s="40" t="n">
+      <c r="K48" s="31" t="n">
         <v>330900</v>
       </c>
-      <c r="L48" s="40">
+      <c r="L48" s="31">
         <f>I48+J48+K48</f>
         <v/>
       </c>
@@ -7166,25 +6508,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F49" s="37" t="n">
+      <c r="F49" s="28" t="n">
         <v>4500000</v>
       </c>
       <c r="G49" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="H49" s="37" t="n">
+      <c r="H49" s="28" t="n">
         <v>39200000</v>
       </c>
-      <c r="I49" s="37" t="n">
+      <c r="I49" s="28" t="n">
         <v>8700000</v>
       </c>
-      <c r="J49" s="37" t="n">
+      <c r="J49" s="28" t="n">
         <v>33400</v>
       </c>
-      <c r="K49" s="37" t="n">
+      <c r="K49" s="28" t="n">
         <v>69300</v>
       </c>
-      <c r="L49" s="37">
+      <c r="L49" s="28">
         <f>I49+J49+K49</f>
         <v/>
       </c>
@@ -7211,45 +6553,45 @@
       <c r="A50" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>@daddyming</t>
         </is>
       </c>
-      <c r="C50" s="39" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>DADDY MING</t>
         </is>
       </c>
-      <c r="D50" s="39" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E50" s="39" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F50" s="40" t="n">
+      <c r="F50" s="31" t="n">
         <v>8700000</v>
       </c>
       <c r="G50" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="H50" s="40" t="n">
+      <c r="H50" s="31" t="n">
         <v>88200000</v>
       </c>
-      <c r="I50" s="40" t="n">
+      <c r="I50" s="31" t="n">
         <v>8700000</v>
       </c>
-      <c r="J50" s="40" t="n">
+      <c r="J50" s="31" t="n">
         <v>91500</v>
       </c>
-      <c r="K50" s="40" t="n">
+      <c r="K50" s="31" t="n">
         <v>17100</v>
       </c>
-      <c r="L50" s="40">
+      <c r="L50" s="31">
         <f>I50+J50+K50</f>
         <v/>
       </c>
@@ -7296,25 +6638,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F51" s="37" t="n">
+      <c r="F51" s="28" t="n">
         <v>376200</v>
       </c>
       <c r="G51" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="H51" s="37" t="n">
+      <c r="H51" s="28" t="n">
         <v>40200000</v>
       </c>
-      <c r="I51" s="37" t="n">
+      <c r="I51" s="28" t="n">
         <v>8600000</v>
       </c>
-      <c r="J51" s="37" t="n">
+      <c r="J51" s="28" t="n">
         <v>58100</v>
       </c>
-      <c r="K51" s="37" t="n">
+      <c r="K51" s="28" t="n">
         <v>134900</v>
       </c>
-      <c r="L51" s="37">
+      <c r="L51" s="28">
         <f>I51+J51+K51</f>
         <v/>
       </c>
@@ -7341,45 +6683,45 @@
       <c r="A52" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>@herodw</t>
         </is>
       </c>
-      <c r="C52" s="39" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>Hero DW</t>
         </is>
       </c>
-      <c r="D52" s="39" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E52" s="39" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F52" s="40" t="n">
+      <c r="F52" s="31" t="n">
         <v>5200000</v>
       </c>
       <c r="G52" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="H52" s="40" t="n">
+      <c r="H52" s="31" t="n">
         <v>40200000</v>
       </c>
-      <c r="I52" s="40" t="n">
+      <c r="I52" s="31" t="n">
         <v>8600000</v>
       </c>
-      <c r="J52" s="40" t="n">
+      <c r="J52" s="31" t="n">
         <v>43300</v>
       </c>
-      <c r="K52" s="40" t="n">
+      <c r="K52" s="31" t="n">
         <v>56800</v>
       </c>
-      <c r="L52" s="40">
+      <c r="L52" s="31">
         <f>I52+J52+K52</f>
         <v/>
       </c>
@@ -7426,25 +6768,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F53" s="37" t="n">
+      <c r="F53" s="28" t="n">
         <v>27400000</v>
       </c>
       <c r="G53" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="H53" s="37" t="n">
+      <c r="H53" s="28" t="n">
         <v>45800000</v>
       </c>
-      <c r="I53" s="37" t="n">
+      <c r="I53" s="28" t="n">
         <v>8400000</v>
       </c>
-      <c r="J53" s="37" t="n">
+      <c r="J53" s="28" t="n">
         <v>69000</v>
       </c>
-      <c r="K53" s="37" t="n">
+      <c r="K53" s="28" t="n">
         <v>57200</v>
       </c>
-      <c r="L53" s="37">
+      <c r="L53" s="28">
         <f>I53+J53+K53</f>
         <v/>
       </c>
@@ -7471,45 +6813,45 @@
       <c r="A54" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="39" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
         <is>
           <t>@samayranarula</t>
         </is>
       </c>
-      <c r="C54" s="39" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>Vinay Narula</t>
         </is>
       </c>
-      <c r="D54" s="39" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E54" s="39" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F54" s="40" t="n">
+      <c r="F54" s="31" t="n">
         <v>4500000</v>
       </c>
       <c r="G54" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="H54" s="40" t="n">
+      <c r="H54" s="31" t="n">
         <v>123200000</v>
       </c>
-      <c r="I54" s="40" t="n">
+      <c r="I54" s="31" t="n">
         <v>8400000</v>
       </c>
-      <c r="J54" s="40" t="n">
+      <c r="J54" s="31" t="n">
         <v>17700</v>
       </c>
-      <c r="K54" s="40" t="n">
+      <c r="K54" s="31" t="n">
         <v>152800</v>
       </c>
-      <c r="L54" s="40">
+      <c r="L54" s="31">
         <f>I54+J54+K54</f>
         <v/>
       </c>
@@ -7556,25 +6898,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F55" s="37" t="n">
+      <c r="F55" s="28" t="n">
         <v>7300000</v>
       </c>
       <c r="G55" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="H55" s="37" t="n">
+      <c r="H55" s="28" t="n">
         <v>56600000</v>
       </c>
-      <c r="I55" s="37" t="n">
+      <c r="I55" s="28" t="n">
         <v>8300000</v>
       </c>
-      <c r="J55" s="37" t="n">
+      <c r="J55" s="28" t="n">
         <v>55900</v>
       </c>
-      <c r="K55" s="37" t="n">
+      <c r="K55" s="28" t="n">
         <v>414200</v>
       </c>
-      <c r="L55" s="37">
+      <c r="L55" s="28">
         <f>I55+J55+K55</f>
         <v/>
       </c>
@@ -7601,45 +6943,45 @@
       <c r="A56" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>@jinsol_oh</t>
         </is>
       </c>
-      <c r="C56" s="39" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>jinsol_oh</t>
         </is>
       </c>
-      <c r="D56" s="39" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E56" s="39" t="inlineStr">
+      <c r="E56" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F56" s="40" t="n">
+      <c r="F56" s="31" t="n">
         <v>4400000</v>
       </c>
       <c r="G56" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="H56" s="40" t="n">
+      <c r="H56" s="31" t="n">
         <v>44500000</v>
       </c>
-      <c r="I56" s="40" t="n">
+      <c r="I56" s="31" t="n">
         <v>8300000</v>
       </c>
-      <c r="J56" s="40" t="n">
+      <c r="J56" s="31" t="n">
         <v>93800</v>
       </c>
-      <c r="K56" s="40" t="n">
+      <c r="K56" s="31" t="n">
         <v>290600</v>
       </c>
-      <c r="L56" s="40">
+      <c r="L56" s="31">
         <f>I56+J56+K56</f>
         <v/>
       </c>
@@ -7686,25 +7028,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F57" s="37" t="n">
+      <c r="F57" s="28" t="n">
         <v>499800</v>
       </c>
       <c r="G57" s="20" t="n">
         <v>170</v>
       </c>
-      <c r="H57" s="37" t="n">
+      <c r="H57" s="28" t="n">
         <v>28800000</v>
       </c>
-      <c r="I57" s="37" t="n">
+      <c r="I57" s="28" t="n">
         <v>8200000</v>
       </c>
-      <c r="J57" s="37" t="n">
+      <c r="J57" s="28" t="n">
         <v>74600</v>
       </c>
-      <c r="K57" s="37" t="n">
+      <c r="K57" s="28" t="n">
         <v>227600</v>
       </c>
-      <c r="L57" s="37">
+      <c r="L57" s="28">
         <f>I57+J57+K57</f>
         <v/>
       </c>
@@ -7731,45 +7073,45 @@
       <c r="A58" s="25" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>@samuelgrubbs</t>
         </is>
       </c>
-      <c r="C58" s="39" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
         <is>
           <t>Samuel Grubbs</t>
         </is>
       </c>
-      <c r="D58" s="39" t="inlineStr">
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E58" s="39" t="inlineStr">
+      <c r="E58" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F58" s="40" t="n">
+      <c r="F58" s="31" t="n">
         <v>7900000</v>
       </c>
       <c r="G58" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="H58" s="40" t="n">
+      <c r="H58" s="31" t="n">
         <v>46800000</v>
       </c>
-      <c r="I58" s="40" t="n">
+      <c r="I58" s="31" t="n">
         <v>8100000</v>
       </c>
-      <c r="J58" s="40" t="n">
+      <c r="J58" s="31" t="n">
         <v>44300</v>
       </c>
-      <c r="K58" s="40" t="n">
+      <c r="K58" s="31" t="n">
         <v>268400</v>
       </c>
-      <c r="L58" s="40">
+      <c r="L58" s="31">
         <f>I58+J58+K58</f>
         <v/>
       </c>
@@ -7816,25 +7158,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F59" s="37" t="n">
+      <c r="F59" s="28" t="n">
         <v>1400000</v>
       </c>
       <c r="G59" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H59" s="37" t="n">
+      <c r="H59" s="28" t="n">
         <v>50900000</v>
       </c>
-      <c r="I59" s="37" t="n">
+      <c r="I59" s="28" t="n">
         <v>8100000</v>
       </c>
-      <c r="J59" s="37" t="n">
+      <c r="J59" s="28" t="n">
         <v>64900</v>
       </c>
-      <c r="K59" s="37" t="n">
+      <c r="K59" s="28" t="n">
         <v>276100</v>
       </c>
-      <c r="L59" s="37">
+      <c r="L59" s="28">
         <f>I59+J59+K59</f>
         <v/>
       </c>
@@ -7861,45 +7203,45 @@
       <c r="A60" s="25" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="39" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>@charliethechipmunk</t>
         </is>
       </c>
-      <c r="C60" s="39" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
         <is>
           <t>Charlie</t>
         </is>
       </c>
-      <c r="D60" s="39" t="inlineStr">
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E60" s="39" t="inlineStr">
+      <c r="E60" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F60" s="40" t="n">
+      <c r="F60" s="31" t="n">
         <v>2400000</v>
       </c>
       <c r="G60" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="H60" s="40" t="n">
+      <c r="H60" s="31" t="n">
         <v>77000000</v>
       </c>
-      <c r="I60" s="40" t="n">
+      <c r="I60" s="31" t="n">
         <v>8000000</v>
       </c>
-      <c r="J60" s="40" t="n">
+      <c r="J60" s="31" t="n">
         <v>63100</v>
       </c>
-      <c r="K60" s="40" t="n">
+      <c r="K60" s="31" t="n">
         <v>131900</v>
       </c>
-      <c r="L60" s="40">
+      <c r="L60" s="31">
         <f>I60+J60+K60</f>
         <v/>
       </c>
@@ -7946,25 +7288,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F61" s="37" t="n">
+      <c r="F61" s="28" t="n">
         <v>1100000</v>
       </c>
       <c r="G61" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="H61" s="37" t="n">
+      <c r="H61" s="28" t="n">
         <v>100600000</v>
       </c>
-      <c r="I61" s="37" t="n">
+      <c r="I61" s="28" t="n">
         <v>7900000</v>
       </c>
-      <c r="J61" s="37" t="n">
+      <c r="J61" s="28" t="n">
         <v>80400</v>
       </c>
-      <c r="K61" s="37" t="n">
+      <c r="K61" s="28" t="n">
         <v>488400</v>
       </c>
-      <c r="L61" s="37">
+      <c r="L61" s="28">
         <f>I61+J61+K61</f>
         <v/>
       </c>
@@ -7991,45 +7333,45 @@
       <c r="A62" s="25" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="39" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>@garnergang5x</t>
         </is>
       </c>
-      <c r="C62" s="39" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>The Garner Family</t>
         </is>
       </c>
-      <c r="D62" s="39" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E62" s="39" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F62" s="40" t="n">
+      <c r="F62" s="31" t="n">
         <v>533300</v>
       </c>
       <c r="G62" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="H62" s="40" t="n">
+      <c r="H62" s="31" t="n">
         <v>42700000</v>
       </c>
-      <c r="I62" s="40" t="n">
+      <c r="I62" s="31" t="n">
         <v>7800000</v>
       </c>
-      <c r="J62" s="40" t="n">
+      <c r="J62" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="K62" s="40" t="n">
+      <c r="K62" s="31" t="n">
         <v>256300</v>
       </c>
-      <c r="L62" s="40">
+      <c r="L62" s="31">
         <f>I62+J62+K62</f>
         <v/>
       </c>
@@ -8076,25 +7418,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F63" s="37" t="n">
+      <c r="F63" s="28" t="n">
         <v>27400000</v>
       </c>
       <c r="G63" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="H63" s="37" t="n">
+      <c r="H63" s="28" t="n">
         <v>71500000</v>
       </c>
-      <c r="I63" s="37" t="n">
+      <c r="I63" s="28" t="n">
         <v>7800000</v>
       </c>
-      <c r="J63" s="37" t="n">
+      <c r="J63" s="28" t="n">
         <v>47700</v>
       </c>
-      <c r="K63" s="37" t="n">
+      <c r="K63" s="28" t="n">
         <v>43900</v>
       </c>
-      <c r="L63" s="37">
+      <c r="L63" s="28">
         <f>I63+J63+K63</f>
         <v/>
       </c>
@@ -8121,45 +7463,45 @@
       <c r="A64" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="39" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>@vudieuthuy91</t>
         </is>
       </c>
-      <c r="C64" s="39" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Vũ Diệu Thuý</t>
         </is>
       </c>
-      <c r="D64" s="39" t="inlineStr">
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E64" s="39" t="inlineStr">
+      <c r="E64" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F64" s="40" t="n">
+      <c r="F64" s="31" t="n">
         <v>1900000</v>
       </c>
       <c r="G64" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="H64" s="40" t="n">
+      <c r="H64" s="31" t="n">
         <v>142900000</v>
       </c>
-      <c r="I64" s="40" t="n">
+      <c r="I64" s="31" t="n">
         <v>7800000</v>
       </c>
-      <c r="J64" s="40" t="n">
+      <c r="J64" s="31" t="n">
         <v>13600</v>
       </c>
-      <c r="K64" s="40" t="n">
+      <c r="K64" s="31" t="n">
         <v>49800</v>
       </c>
-      <c r="L64" s="40">
+      <c r="L64" s="31">
         <f>I64+J64+K64</f>
         <v/>
       </c>
@@ -8206,25 +7548,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F65" s="37" t="n">
+      <c r="F65" s="28" t="n">
         <v>7900000</v>
       </c>
       <c r="G65" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="H65" s="37" t="n">
+      <c r="H65" s="28" t="n">
         <v>50100000</v>
       </c>
-      <c r="I65" s="37" t="n">
+      <c r="I65" s="28" t="n">
         <v>7700000</v>
       </c>
-      <c r="J65" s="37" t="n">
+      <c r="J65" s="28" t="n">
         <v>85600</v>
       </c>
-      <c r="K65" s="37" t="n">
+      <c r="K65" s="28" t="n">
         <v>198400</v>
       </c>
-      <c r="L65" s="37">
+      <c r="L65" s="28">
         <f>I65+J65+K65</f>
         <v/>
       </c>
@@ -8251,45 +7593,45 @@
       <c r="A66" s="25" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="39" t="inlineStr">
+      <c r="B66" s="30" t="inlineStr">
         <is>
           <t>@unreleased.polog</t>
         </is>
       </c>
-      <c r="C66" s="39" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>Yath Alectha</t>
         </is>
       </c>
-      <c r="D66" s="39" t="inlineStr">
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E66" s="39" t="inlineStr">
+      <c r="E66" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F66" s="40" t="n">
+      <c r="F66" s="31" t="n">
         <v>257600</v>
       </c>
       <c r="G66" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="H66" s="40" t="n">
+      <c r="H66" s="31" t="n">
         <v>36000000</v>
       </c>
-      <c r="I66" s="40" t="n">
+      <c r="I66" s="31" t="n">
         <v>7700000</v>
       </c>
-      <c r="J66" s="40" t="n">
+      <c r="J66" s="31" t="n">
         <v>69400</v>
       </c>
-      <c r="K66" s="40" t="n">
+      <c r="K66" s="31" t="n">
         <v>226400</v>
       </c>
-      <c r="L66" s="40">
+      <c r="L66" s="31">
         <f>I66+J66+K66</f>
         <v/>
       </c>
@@ -8336,25 +7678,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F67" s="37" t="n">
+      <c r="F67" s="28" t="n">
         <v>10500000</v>
       </c>
       <c r="G67" s="20" t="n">
         <v>43</v>
       </c>
-      <c r="H67" s="37" t="n">
+      <c r="H67" s="28" t="n">
         <v>30500000</v>
       </c>
-      <c r="I67" s="37" t="n">
+      <c r="I67" s="28" t="n">
         <v>7700000</v>
       </c>
-      <c r="J67" s="37" t="n">
+      <c r="J67" s="28" t="n">
         <v>56200</v>
       </c>
-      <c r="K67" s="37" t="n">
+      <c r="K67" s="28" t="n">
         <v>202800</v>
       </c>
-      <c r="L67" s="37">
+      <c r="L67" s="28">
         <f>I67+J67+K67</f>
         <v/>
       </c>
@@ -8381,45 +7723,45 @@
       <c r="A68" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="39" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>@maliksizzlee</t>
         </is>
       </c>
-      <c r="C68" s="39" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>Malik</t>
         </is>
       </c>
-      <c r="D68" s="39" t="inlineStr">
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E68" s="39" t="inlineStr">
+      <c r="E68" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F68" s="40" t="n">
+      <c r="F68" s="31" t="n">
         <v>516000</v>
       </c>
       <c r="G68" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H68" s="40" t="n">
+      <c r="H68" s="31" t="n">
         <v>40800000</v>
       </c>
-      <c r="I68" s="40" t="n">
+      <c r="I68" s="31" t="n">
         <v>7700000</v>
       </c>
-      <c r="J68" s="40" t="n">
+      <c r="J68" s="31" t="n">
         <v>55300</v>
       </c>
-      <c r="K68" s="40" t="n">
+      <c r="K68" s="31" t="n">
         <v>620400</v>
       </c>
-      <c r="L68" s="40">
+      <c r="L68" s="31">
         <f>I68+J68+K68</f>
         <v/>
       </c>
@@ -8466,25 +7808,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F69" s="37" t="n">
+      <c r="F69" s="28" t="n">
         <v>8700000</v>
       </c>
       <c r="G69" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="H69" s="37" t="n">
+      <c r="H69" s="28" t="n">
         <v>50700000</v>
       </c>
-      <c r="I69" s="37" t="n">
+      <c r="I69" s="28" t="n">
         <v>7600000</v>
       </c>
-      <c r="J69" s="37" t="n">
+      <c r="J69" s="28" t="n">
         <v>77100</v>
       </c>
-      <c r="K69" s="37" t="n">
+      <c r="K69" s="28" t="n">
         <v>478500</v>
       </c>
-      <c r="L69" s="37">
+      <c r="L69" s="28">
         <f>I69+J69+K69</f>
         <v/>
       </c>
@@ -8511,45 +7853,45 @@
       <c r="A70" s="25" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="39" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>@tizilwa</t>
         </is>
       </c>
-      <c r="C70" s="39" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Dilkash Dhany Ramn</t>
         </is>
       </c>
-      <c r="D70" s="39" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E70" s="39" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F70" s="40" t="n">
+      <c r="F70" s="31" t="n">
         <v>1300000</v>
       </c>
       <c r="G70" s="25" t="n">
         <v>56</v>
       </c>
-      <c r="H70" s="40" t="n">
+      <c r="H70" s="31" t="n">
         <v>102000000</v>
       </c>
-      <c r="I70" s="40" t="n">
+      <c r="I70" s="31" t="n">
         <v>7600000</v>
       </c>
-      <c r="J70" s="40" t="n">
+      <c r="J70" s="31" t="n">
         <v>114600</v>
       </c>
-      <c r="K70" s="40" t="n">
+      <c r="K70" s="31" t="n">
         <v>473400</v>
       </c>
-      <c r="L70" s="40">
+      <c r="L70" s="31">
         <f>I70+J70+K70</f>
         <v/>
       </c>
@@ -8596,25 +7938,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F71" s="37" t="n">
+      <c r="F71" s="28" t="n">
         <v>398400</v>
       </c>
       <c r="G71" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="H71" s="37" t="n">
+      <c r="H71" s="28" t="n">
         <v>97200000</v>
       </c>
-      <c r="I71" s="37" t="n">
+      <c r="I71" s="28" t="n">
         <v>7600000</v>
       </c>
-      <c r="J71" s="37" t="n">
+      <c r="J71" s="28" t="n">
         <v>44500</v>
       </c>
-      <c r="K71" s="37" t="n">
+      <c r="K71" s="28" t="n">
         <v>66600</v>
       </c>
-      <c r="L71" s="37">
+      <c r="L71" s="28">
         <f>I71+J71+K71</f>
         <v/>
       </c>
@@ -8641,45 +7983,45 @@
       <c r="A72" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="39" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>@relaxedbryan</t>
         </is>
       </c>
-      <c r="C72" s="39" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
         <is>
           <t>Relaxed Bryan</t>
         </is>
       </c>
-      <c r="D72" s="39" t="inlineStr">
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E72" s="39" t="inlineStr">
+      <c r="E72" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F72" s="40" t="n">
+      <c r="F72" s="31" t="n">
         <v>1900000</v>
       </c>
       <c r="G72" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="H72" s="40" t="n">
+      <c r="H72" s="31" t="n">
         <v>142000000</v>
       </c>
-      <c r="I72" s="40" t="n">
+      <c r="I72" s="31" t="n">
         <v>7600000</v>
       </c>
-      <c r="J72" s="40" t="n">
+      <c r="J72" s="31" t="n">
         <v>63200</v>
       </c>
-      <c r="K72" s="40" t="n">
+      <c r="K72" s="31" t="n">
         <v>711800</v>
       </c>
-      <c r="L72" s="40">
+      <c r="L72" s="31">
         <f>I72+J72+K72</f>
         <v/>
       </c>
@@ -8726,25 +8068,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F73" s="37" t="n">
+      <c r="F73" s="28" t="n">
         <v>824700</v>
       </c>
       <c r="G73" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="H73" s="37" t="n">
+      <c r="H73" s="28" t="n">
         <v>49100000</v>
       </c>
-      <c r="I73" s="37" t="n">
+      <c r="I73" s="28" t="n">
         <v>7500000</v>
       </c>
-      <c r="J73" s="37" t="n">
+      <c r="J73" s="28" t="n">
         <v>41200</v>
       </c>
-      <c r="K73" s="37" t="n">
+      <c r="K73" s="28" t="n">
         <v>442500</v>
       </c>
-      <c r="L73" s="37">
+      <c r="L73" s="28">
         <f>I73+J73+K73</f>
         <v/>
       </c>
@@ -8771,45 +8113,45 @@
       <c r="A74" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="39" t="inlineStr">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>@bryanduran100</t>
         </is>
       </c>
-      <c r="C74" s="39" t="inlineStr">
+      <c r="C74" s="30" t="inlineStr">
         <is>
           <t>BRYAN DURAN</t>
         </is>
       </c>
-      <c r="D74" s="39" t="inlineStr">
+      <c r="D74" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E74" s="39" t="inlineStr">
+      <c r="E74" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F74" s="40" t="n">
+      <c r="F74" s="31" t="n">
         <v>4000000</v>
       </c>
       <c r="G74" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="H74" s="40" t="n">
+      <c r="H74" s="31" t="n">
         <v>56400000</v>
       </c>
-      <c r="I74" s="40" t="n">
+      <c r="I74" s="31" t="n">
         <v>7500000</v>
       </c>
-      <c r="J74" s="40" t="n">
+      <c r="J74" s="31" t="n">
         <v>150400</v>
       </c>
-      <c r="K74" s="40" t="n">
+      <c r="K74" s="31" t="n">
         <v>255100</v>
       </c>
-      <c r="L74" s="40">
+      <c r="L74" s="31">
         <f>I74+J74+K74</f>
         <v/>
       </c>
@@ -8856,25 +8198,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F75" s="37" t="n">
+      <c r="F75" s="28" t="n">
         <v>14500000</v>
       </c>
       <c r="G75" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="H75" s="37" t="n">
+      <c r="H75" s="28" t="n">
         <v>59700000</v>
       </c>
-      <c r="I75" s="37" t="n">
+      <c r="I75" s="28" t="n">
         <v>7500000</v>
       </c>
-      <c r="J75" s="37" t="n">
+      <c r="J75" s="28" t="n">
         <v>64100</v>
       </c>
-      <c r="K75" s="37" t="n">
+      <c r="K75" s="28" t="n">
         <v>431600</v>
       </c>
-      <c r="L75" s="37">
+      <c r="L75" s="28">
         <f>I75+J75+K75</f>
         <v/>
       </c>
@@ -8901,45 +8243,45 @@
       <c r="A76" s="25" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="39" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>@joshdub</t>
         </is>
       </c>
-      <c r="C76" s="39" t="inlineStr">
+      <c r="C76" s="30" t="inlineStr">
         <is>
           <t>Joshdub</t>
         </is>
       </c>
-      <c r="D76" s="39" t="inlineStr">
+      <c r="D76" s="30" t="inlineStr">
         <is>
           <t>Sports &amp; Gaming</t>
         </is>
       </c>
-      <c r="E76" s="39" t="inlineStr">
+      <c r="E76" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F76" s="40" t="n">
+      <c r="F76" s="31" t="n">
         <v>8700000</v>
       </c>
       <c r="G76" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H76" s="40" t="n">
+      <c r="H76" s="31" t="n">
         <v>41000000</v>
       </c>
-      <c r="I76" s="40" t="n">
+      <c r="I76" s="31" t="n">
         <v>7400000</v>
       </c>
-      <c r="J76" s="40" t="n">
+      <c r="J76" s="31" t="n">
         <v>37900</v>
       </c>
-      <c r="K76" s="40" t="n">
+      <c r="K76" s="31" t="n">
         <v>291900</v>
       </c>
-      <c r="L76" s="40">
+      <c r="L76" s="31">
         <f>I76+J76+K76</f>
         <v/>
       </c>
@@ -8986,25 +8328,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F77" s="37" t="n">
+      <c r="F77" s="28" t="n">
         <v>1300000</v>
       </c>
       <c r="G77" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H77" s="37" t="n">
+      <c r="H77" s="28" t="n">
         <v>34000000</v>
       </c>
-      <c r="I77" s="37" t="n">
+      <c r="I77" s="28" t="n">
         <v>7400000</v>
       </c>
-      <c r="J77" s="37" t="n">
+      <c r="J77" s="28" t="n">
         <v>91200</v>
       </c>
-      <c r="K77" s="37" t="n">
+      <c r="K77" s="28" t="n">
         <v>464700</v>
       </c>
-      <c r="L77" s="37">
+      <c r="L77" s="28">
         <f>I77+J77+K77</f>
         <v/>
       </c>
@@ -9031,45 +8373,45 @@
       <c r="A78" s="25" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="39" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>@tedandlinda</t>
         </is>
       </c>
-      <c r="C78" s="39" t="inlineStr">
+      <c r="C78" s="30" t="inlineStr">
         <is>
           <t>TedAndLinda</t>
         </is>
       </c>
-      <c r="D78" s="39" t="inlineStr">
+      <c r="D78" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E78" s="39" t="inlineStr">
+      <c r="E78" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F78" s="40" t="n">
+      <c r="F78" s="31" t="n">
         <v>1800000</v>
       </c>
       <c r="G78" s="25" t="n">
         <v>57</v>
       </c>
-      <c r="H78" s="40" t="n">
+      <c r="H78" s="31" t="n">
         <v>38000000</v>
       </c>
-      <c r="I78" s="40" t="n">
+      <c r="I78" s="31" t="n">
         <v>7400000</v>
       </c>
-      <c r="J78" s="40" t="n">
+      <c r="J78" s="31" t="n">
         <v>92800</v>
       </c>
-      <c r="K78" s="40" t="n">
+      <c r="K78" s="31" t="n">
         <v>554700</v>
       </c>
-      <c r="L78" s="40">
+      <c r="L78" s="31">
         <f>I78+J78+K78</f>
         <v/>
       </c>
@@ -9116,25 +8458,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F79" s="37" t="n">
+      <c r="F79" s="28" t="n">
         <v>9100000</v>
       </c>
       <c r="G79" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="H79" s="37" t="n">
+      <c r="H79" s="28" t="n">
         <v>69400000</v>
       </c>
-      <c r="I79" s="37" t="n">
+      <c r="I79" s="28" t="n">
         <v>7400000</v>
       </c>
-      <c r="J79" s="37" t="n">
+      <c r="J79" s="28" t="n">
         <v>14000</v>
       </c>
-      <c r="K79" s="37" t="n">
+      <c r="K79" s="28" t="n">
         <v>81600</v>
       </c>
-      <c r="L79" s="37">
+      <c r="L79" s="28">
         <f>I79+J79+K79</f>
         <v/>
       </c>
@@ -9161,45 +8503,45 @@
       <c r="A80" s="25" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="39" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>@orzutiextra</t>
         </is>
       </c>
-      <c r="C80" s="39" t="inlineStr">
+      <c r="C80" s="30" t="inlineStr">
         <is>
           <t>Or Zuti</t>
         </is>
       </c>
-      <c r="D80" s="39" t="inlineStr">
+      <c r="D80" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E80" s="39" t="inlineStr">
+      <c r="E80" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F80" s="40" t="n">
+      <c r="F80" s="31" t="n">
         <v>5700000</v>
       </c>
       <c r="G80" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H80" s="40" t="n">
+      <c r="H80" s="31" t="n">
         <v>53100000</v>
       </c>
-      <c r="I80" s="40" t="n">
+      <c r="I80" s="31" t="n">
         <v>7300000</v>
       </c>
-      <c r="J80" s="40" t="n">
+      <c r="J80" s="31" t="n">
         <v>12600</v>
       </c>
-      <c r="K80" s="40" t="n">
+      <c r="K80" s="31" t="n">
         <v>21200</v>
       </c>
-      <c r="L80" s="40">
+      <c r="L80" s="31">
         <f>I80+J80+K80</f>
         <v/>
       </c>
@@ -9246,25 +8588,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F81" s="37" t="n">
+      <c r="F81" s="28" t="n">
         <v>2300000</v>
       </c>
       <c r="G81" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="H81" s="37" t="n">
+      <c r="H81" s="28" t="n">
         <v>86200000</v>
       </c>
-      <c r="I81" s="37" t="n">
+      <c r="I81" s="28" t="n">
         <v>7300000</v>
       </c>
-      <c r="J81" s="37" t="n">
+      <c r="J81" s="28" t="n">
         <v>16300</v>
       </c>
-      <c r="K81" s="37" t="n">
+      <c r="K81" s="28" t="n">
         <v>8102</v>
       </c>
-      <c r="L81" s="37">
+      <c r="L81" s="28">
         <f>I81+J81+K81</f>
         <v/>
       </c>
@@ -9291,45 +8633,45 @@
       <c r="A82" s="25" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="39" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>@itsjennaraine</t>
         </is>
       </c>
-      <c r="C82" s="39" t="inlineStr">
+      <c r="C82" s="30" t="inlineStr">
         <is>
           <t>jenna raine</t>
         </is>
       </c>
-      <c r="D82" s="39" t="inlineStr">
+      <c r="D82" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E82" s="39" t="inlineStr">
+      <c r="E82" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F82" s="40" t="n">
+      <c r="F82" s="31" t="n">
         <v>1100000</v>
       </c>
       <c r="G82" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="H82" s="40" t="n">
+      <c r="H82" s="31" t="n">
         <v>38300000</v>
       </c>
-      <c r="I82" s="40" t="n">
+      <c r="I82" s="31" t="n">
         <v>7300000</v>
       </c>
-      <c r="J82" s="40" t="n">
+      <c r="J82" s="31" t="n">
         <v>37300</v>
       </c>
-      <c r="K82" s="40" t="n">
+      <c r="K82" s="31" t="n">
         <v>173800</v>
       </c>
-      <c r="L82" s="40">
+      <c r="L82" s="31">
         <f>I82+J82+K82</f>
         <v/>
       </c>
@@ -9376,25 +8718,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F83" s="37" t="n">
+      <c r="F83" s="28" t="n">
         <v>6900000</v>
       </c>
       <c r="G83" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="H83" s="37" t="n">
+      <c r="H83" s="28" t="n">
         <v>50500000</v>
       </c>
-      <c r="I83" s="37" t="n">
+      <c r="I83" s="28" t="n">
         <v>7200000</v>
       </c>
-      <c r="J83" s="37" t="n">
+      <c r="J83" s="28" t="n">
         <v>37300</v>
       </c>
-      <c r="K83" s="37" t="n">
+      <c r="K83" s="28" t="n">
         <v>227600</v>
       </c>
-      <c r="L83" s="37">
+      <c r="L83" s="28">
         <f>I83+J83+K83</f>
         <v/>
       </c>
@@ -9421,45 +8763,45 @@
       <c r="A84" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="39" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>@kyleandjade_</t>
         </is>
       </c>
-      <c r="C84" s="39" t="inlineStr">
+      <c r="C84" s="30" t="inlineStr">
         <is>
           <t>Kyle and Jade</t>
         </is>
       </c>
-      <c r="D84" s="39" t="inlineStr">
+      <c r="D84" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E84" s="39" t="inlineStr">
+      <c r="E84" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F84" s="40" t="n">
+      <c r="F84" s="31" t="n">
         <v>4500000</v>
       </c>
       <c r="G84" s="25" t="n">
         <v>35</v>
       </c>
-      <c r="H84" s="40" t="n">
+      <c r="H84" s="31" t="n">
         <v>40100000</v>
       </c>
-      <c r="I84" s="40" t="n">
+      <c r="I84" s="31" t="n">
         <v>7100000</v>
       </c>
-      <c r="J84" s="40" t="n">
+      <c r="J84" s="31" t="n">
         <v>71800</v>
       </c>
-      <c r="K84" s="40" t="n">
+      <c r="K84" s="31" t="n">
         <v>375800</v>
       </c>
-      <c r="L84" s="40">
+      <c r="L84" s="31">
         <f>I84+J84+K84</f>
         <v/>
       </c>
@@ -9506,25 +8848,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F85" s="37" t="n">
+      <c r="F85" s="28" t="n">
         <v>287800</v>
       </c>
       <c r="G85" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H85" s="37" t="n">
+      <c r="H85" s="28" t="n">
         <v>49200000</v>
       </c>
-      <c r="I85" s="37" t="n">
+      <c r="I85" s="28" t="n">
         <v>7100000</v>
       </c>
-      <c r="J85" s="37" t="n">
+      <c r="J85" s="28" t="n">
         <v>27500</v>
       </c>
-      <c r="K85" s="37" t="n">
+      <c r="K85" s="28" t="n">
         <v>19400</v>
       </c>
-      <c r="L85" s="37">
+      <c r="L85" s="28">
         <f>I85+J85+K85</f>
         <v/>
       </c>
@@ -9551,45 +8893,45 @@
       <c r="A86" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="39" t="inlineStr">
+      <c r="B86" s="30" t="inlineStr">
         <is>
           <t>@the89min</t>
         </is>
       </c>
-      <c r="C86" s="39" t="inlineStr">
+      <c r="C86" s="30" t="inlineStr">
         <is>
           <t>Football One Love</t>
         </is>
       </c>
-      <c r="D86" s="39" t="inlineStr">
+      <c r="D86" s="30" t="inlineStr">
         <is>
           <t>Sports &amp; Gaming</t>
         </is>
       </c>
-      <c r="E86" s="39" t="inlineStr">
+      <c r="E86" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F86" s="40" t="n">
+      <c r="F86" s="31" t="n">
         <v>961200</v>
       </c>
       <c r="G86" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="H86" s="40" t="n">
+      <c r="H86" s="31" t="n">
         <v>51500000</v>
       </c>
-      <c r="I86" s="40" t="n">
+      <c r="I86" s="31" t="n">
         <v>7100000</v>
       </c>
-      <c r="J86" s="40" t="n">
+      <c r="J86" s="31" t="n">
         <v>32100</v>
       </c>
-      <c r="K86" s="40" t="n">
+      <c r="K86" s="31" t="n">
         <v>156400</v>
       </c>
-      <c r="L86" s="40">
+      <c r="L86" s="31">
         <f>I86+J86+K86</f>
         <v/>
       </c>
@@ -9636,25 +8978,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F87" s="37" t="n">
+      <c r="F87" s="28" t="n">
         <v>4400000</v>
       </c>
       <c r="G87" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="H87" s="37" t="n">
+      <c r="H87" s="28" t="n">
         <v>35200000</v>
       </c>
-      <c r="I87" s="37" t="n">
+      <c r="I87" s="28" t="n">
         <v>7100000</v>
       </c>
-      <c r="J87" s="37" t="n">
+      <c r="J87" s="28" t="n">
         <v>75000</v>
       </c>
-      <c r="K87" s="37" t="n">
+      <c r="K87" s="28" t="n">
         <v>105200</v>
       </c>
-      <c r="L87" s="37">
+      <c r="L87" s="28">
         <f>I87+J87+K87</f>
         <v/>
       </c>
@@ -9681,45 +9023,45 @@
       <c r="A88" s="25" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="39" t="inlineStr">
+      <c r="B88" s="30" t="inlineStr">
         <is>
           <t>@scottish_mychka</t>
         </is>
       </c>
-      <c r="C88" s="39" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>Mychka</t>
         </is>
       </c>
-      <c r="D88" s="39" t="inlineStr">
+      <c r="D88" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E88" s="39" t="inlineStr">
+      <c r="E88" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F88" s="40" t="n">
+      <c r="F88" s="31" t="n">
         <v>475800</v>
       </c>
       <c r="G88" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="H88" s="40" t="n">
+      <c r="H88" s="31" t="n">
         <v>38400000</v>
       </c>
-      <c r="I88" s="40" t="n">
+      <c r="I88" s="31" t="n">
         <v>7100000</v>
       </c>
-      <c r="J88" s="40" t="n">
+      <c r="J88" s="31" t="n">
         <v>77800</v>
       </c>
-      <c r="K88" s="40" t="n">
+      <c r="K88" s="31" t="n">
         <v>253100</v>
       </c>
-      <c r="L88" s="40">
+      <c r="L88" s="31">
         <f>I88+J88+K88</f>
         <v/>
       </c>
@@ -9766,25 +9108,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F89" s="37" t="n">
+      <c r="F89" s="28" t="n">
         <v>550300</v>
       </c>
       <c r="G89" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="H89" s="37" t="n">
+      <c r="H89" s="28" t="n">
         <v>55200000</v>
       </c>
-      <c r="I89" s="37" t="n">
+      <c r="I89" s="28" t="n">
         <v>7100000</v>
       </c>
-      <c r="J89" s="37" t="n">
+      <c r="J89" s="28" t="n">
         <v>30500</v>
       </c>
-      <c r="K89" s="37" t="n">
+      <c r="K89" s="28" t="n">
         <v>89700</v>
       </c>
-      <c r="L89" s="37">
+      <c r="L89" s="28">
         <f>I89+J89+K89</f>
         <v/>
       </c>
@@ -9811,45 +9153,45 @@
       <c r="A90" s="25" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="39" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
         <is>
           <t>@thismightbeyasmina</t>
         </is>
       </c>
-      <c r="C90" s="39" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>yasmina vakili</t>
         </is>
       </c>
-      <c r="D90" s="39" t="inlineStr">
+      <c r="D90" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E90" s="39" t="inlineStr">
+      <c r="E90" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F90" s="40" t="n">
+      <c r="F90" s="31" t="n">
         <v>74300</v>
       </c>
       <c r="G90" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="H90" s="40" t="n">
+      <c r="H90" s="31" t="n">
         <v>31500000</v>
       </c>
-      <c r="I90" s="40" t="n">
+      <c r="I90" s="31" t="n">
         <v>7000000</v>
       </c>
-      <c r="J90" s="40" t="n">
+      <c r="J90" s="31" t="n">
         <v>48300</v>
       </c>
-      <c r="K90" s="40" t="n">
+      <c r="K90" s="31" t="n">
         <v>150400</v>
       </c>
-      <c r="L90" s="40">
+      <c r="L90" s="31">
         <f>I90+J90+K90</f>
         <v/>
       </c>
@@ -9896,25 +9238,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F91" s="37" t="n">
+      <c r="F91" s="28" t="n">
         <v>437300</v>
       </c>
       <c r="G91" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="H91" s="37" t="n">
+      <c r="H91" s="28" t="n">
         <v>34100000</v>
       </c>
-      <c r="I91" s="37" t="n">
+      <c r="I91" s="28" t="n">
         <v>7000000</v>
       </c>
-      <c r="J91" s="37" t="n">
+      <c r="J91" s="28" t="n">
         <v>25500</v>
       </c>
-      <c r="K91" s="37" t="n">
+      <c r="K91" s="28" t="n">
         <v>33600</v>
       </c>
-      <c r="L91" s="37">
+      <c r="L91" s="28">
         <f>I91+J91+K91</f>
         <v/>
       </c>
@@ -9941,45 +9283,45 @@
       <c r="A92" s="25" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="39" t="inlineStr">
+      <c r="B92" s="30" t="inlineStr">
         <is>
           <t>@lastminute_21</t>
         </is>
       </c>
-      <c r="C92" s="39" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>lastMinute_21</t>
         </is>
       </c>
-      <c r="D92" s="39" t="inlineStr">
+      <c r="D92" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E92" s="39" t="inlineStr">
+      <c r="E92" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F92" s="40" t="n">
+      <c r="F92" s="31" t="n">
         <v>4500000</v>
       </c>
       <c r="G92" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H92" s="40" t="n">
+      <c r="H92" s="31" t="n">
         <v>79400000</v>
       </c>
-      <c r="I92" s="40" t="n">
+      <c r="I92" s="31" t="n">
         <v>7000000</v>
       </c>
-      <c r="J92" s="40" t="n">
+      <c r="J92" s="31" t="n">
         <v>9796</v>
       </c>
-      <c r="K92" s="40" t="n">
+      <c r="K92" s="31" t="n">
         <v>182100</v>
       </c>
-      <c r="L92" s="40">
+      <c r="L92" s="31">
         <f>I92+J92+K92</f>
         <v/>
       </c>
@@ -10026,25 +9368,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F93" s="37" t="n">
+      <c r="F93" s="28" t="n">
         <v>1800000</v>
       </c>
       <c r="G93" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="H93" s="37" t="n">
+      <c r="H93" s="28" t="n">
         <v>70700000</v>
       </c>
-      <c r="I93" s="37" t="n">
+      <c r="I93" s="28" t="n">
         <v>7000000</v>
       </c>
-      <c r="J93" s="37" t="n">
+      <c r="J93" s="28" t="n">
         <v>60100</v>
       </c>
-      <c r="K93" s="37" t="n">
+      <c r="K93" s="28" t="n">
         <v>262900</v>
       </c>
-      <c r="L93" s="37">
+      <c r="L93" s="28">
         <f>I93+J93+K93</f>
         <v/>
       </c>
@@ -10071,45 +9413,45 @@
       <c r="A94" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="39" t="inlineStr">
+      <c r="B94" s="30" t="inlineStr">
         <is>
           <t>@ace.central</t>
         </is>
       </c>
-      <c r="C94" s="39" t="inlineStr">
+      <c r="C94" s="30" t="inlineStr">
         <is>
           <t>Ace Central</t>
         </is>
       </c>
-      <c r="D94" s="39" t="inlineStr">
+      <c r="D94" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E94" s="39" t="inlineStr">
+      <c r="E94" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F94" s="40" t="n">
+      <c r="F94" s="31" t="n">
         <v>294800</v>
       </c>
       <c r="G94" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="H94" s="40" t="n">
+      <c r="H94" s="31" t="n">
         <v>48700000</v>
       </c>
-      <c r="I94" s="40" t="n">
+      <c r="I94" s="31" t="n">
         <v>7000000</v>
       </c>
-      <c r="J94" s="40" t="n">
+      <c r="J94" s="31" t="n">
         <v>86800</v>
       </c>
-      <c r="K94" s="40" t="n">
+      <c r="K94" s="31" t="n">
         <v>256400</v>
       </c>
-      <c r="L94" s="40">
+      <c r="L94" s="31">
         <f>I94+J94+K94</f>
         <v/>
       </c>
@@ -10156,25 +9498,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F95" s="37" t="n">
+      <c r="F95" s="28" t="n">
         <v>3600000</v>
       </c>
       <c r="G95" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="H95" s="37" t="n">
+      <c r="H95" s="28" t="n">
         <v>49800000</v>
       </c>
-      <c r="I95" s="37" t="n">
+      <c r="I95" s="28" t="n">
         <v>7000000</v>
       </c>
-      <c r="J95" s="37" t="n">
+      <c r="J95" s="28" t="n">
         <v>11100</v>
       </c>
-      <c r="K95" s="37" t="n">
+      <c r="K95" s="28" t="n">
         <v>40800</v>
       </c>
-      <c r="L95" s="37">
+      <c r="L95" s="28">
         <f>I95+J95+K95</f>
         <v/>
       </c>
@@ -10201,45 +9543,45 @@
       <c r="A96" s="25" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="39" t="inlineStr">
+      <c r="B96" s="30" t="inlineStr">
         <is>
           <t>@jinsol_oh</t>
         </is>
       </c>
-      <c r="C96" s="39" t="inlineStr">
+      <c r="C96" s="30" t="inlineStr">
         <is>
           <t>jinsol_oh</t>
         </is>
       </c>
-      <c r="D96" s="39" t="inlineStr">
+      <c r="D96" s="30" t="inlineStr">
         <is>
           <t>Famille &amp; Couple</t>
         </is>
       </c>
-      <c r="E96" s="39" t="inlineStr">
+      <c r="E96" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F96" s="40" t="n">
+      <c r="F96" s="31" t="n">
         <v>4400000</v>
       </c>
       <c r="G96" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="H96" s="40" t="n">
+      <c r="H96" s="31" t="n">
         <v>48700000</v>
       </c>
-      <c r="I96" s="40" t="n">
+      <c r="I96" s="31" t="n">
         <v>7000000</v>
       </c>
-      <c r="J96" s="40" t="n">
+      <c r="J96" s="31" t="n">
         <v>26700</v>
       </c>
-      <c r="K96" s="40" t="n">
+      <c r="K96" s="31" t="n">
         <v>39600</v>
       </c>
-      <c r="L96" s="40">
+      <c r="L96" s="31">
         <f>I96+J96+K96</f>
         <v/>
       </c>
@@ -10286,25 +9628,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F97" s="37" t="n">
+      <c r="F97" s="28" t="n">
         <v>480700</v>
       </c>
       <c r="G97" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="H97" s="37" t="n">
+      <c r="H97" s="28" t="n">
         <v>43000000</v>
       </c>
-      <c r="I97" s="37" t="n">
+      <c r="I97" s="28" t="n">
         <v>6900000</v>
       </c>
-      <c r="J97" s="37" t="n">
+      <c r="J97" s="28" t="n">
         <v>70800</v>
       </c>
-      <c r="K97" s="37" t="n">
+      <c r="K97" s="28" t="n">
         <v>116200</v>
       </c>
-      <c r="L97" s="37">
+      <c r="L97" s="28">
         <f>I97+J97+K97</f>
         <v/>
       </c>
@@ -10331,45 +9673,45 @@
       <c r="A98" s="25" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="39" t="inlineStr">
+      <c r="B98" s="30" t="inlineStr">
         <is>
           <t>@miyaevarenae</t>
         </is>
       </c>
-      <c r="C98" s="39" t="inlineStr">
+      <c r="C98" s="30" t="inlineStr">
         <is>
           <t>Miyaeva Renae</t>
         </is>
       </c>
-      <c r="D98" s="39" t="inlineStr">
+      <c r="D98" s="30" t="inlineStr">
         <is>
           <t>Humour &amp; Sketch</t>
         </is>
       </c>
-      <c r="E98" s="39" t="inlineStr">
+      <c r="E98" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F98" s="40" t="n">
+      <c r="F98" s="31" t="n">
         <v>5000000</v>
       </c>
       <c r="G98" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="H98" s="40" t="n">
+      <c r="H98" s="31" t="n">
         <v>32600000</v>
       </c>
-      <c r="I98" s="40" t="n">
+      <c r="I98" s="31" t="n">
         <v>6900000</v>
       </c>
-      <c r="J98" s="40" t="n">
+      <c r="J98" s="31" t="n">
         <v>25900</v>
       </c>
-      <c r="K98" s="40" t="n">
+      <c r="K98" s="31" t="n">
         <v>43700</v>
       </c>
-      <c r="L98" s="40">
+      <c r="L98" s="31">
         <f>I98+J98+K98</f>
         <v/>
       </c>
@@ -10416,25 +9758,25 @@
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F99" s="37" t="n">
+      <c r="F99" s="28" t="n">
         <v>19700000</v>
       </c>
       <c r="G99" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="H99" s="37" t="n">
+      <c r="H99" s="28" t="n">
         <v>55400000</v>
       </c>
-      <c r="I99" s="37" t="n">
+      <c r="I99" s="28" t="n">
         <v>6900000</v>
       </c>
-      <c r="J99" s="37" t="n">
+      <c r="J99" s="28" t="n">
         <v>10500</v>
       </c>
-      <c r="K99" s="37" t="n">
+      <c r="K99" s="28" t="n">
         <v>136400</v>
       </c>
-      <c r="L99" s="37">
+      <c r="L99" s="28">
         <f>I99+J99+K99</f>
         <v/>
       </c>
@@ -10461,45 +9803,45 @@
       <c r="A100" s="25" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="39" t="inlineStr">
+      <c r="B100" s="30" t="inlineStr">
         <is>
           <t>@thekiryalife</t>
         </is>
       </c>
-      <c r="C100" s="39" t="inlineStr">
+      <c r="C100" s="30" t="inlineStr">
         <is>
           <t>Kirya Kolesnikov</t>
         </is>
       </c>
-      <c r="D100" s="39" t="inlineStr">
+      <c r="D100" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E100" s="39" t="inlineStr">
+      <c r="E100" s="30" t="inlineStr">
         <is>
           <t>Mega (5M+)</t>
         </is>
       </c>
-      <c r="F100" s="40" t="n">
+      <c r="F100" s="31" t="n">
         <v>33200000</v>
       </c>
       <c r="G100" s="25" t="n">
         <v>59</v>
       </c>
-      <c r="H100" s="40" t="n">
+      <c r="H100" s="31" t="n">
         <v>82300000</v>
       </c>
-      <c r="I100" s="40" t="n">
+      <c r="I100" s="31" t="n">
         <v>6900000</v>
       </c>
-      <c r="J100" s="40" t="n">
+      <c r="J100" s="31" t="n">
         <v>30800</v>
       </c>
-      <c r="K100" s="40" t="n">
+      <c r="K100" s="31" t="n">
         <v>194900</v>
       </c>
-      <c r="L100" s="40">
+      <c r="L100" s="31">
         <f>I100+J100+K100</f>
         <v/>
       </c>
@@ -10546,25 +9888,25 @@
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F101" s="37" t="n">
+      <c r="F101" s="28" t="n">
         <v>3000000</v>
       </c>
       <c r="G101" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="H101" s="37" t="n">
+      <c r="H101" s="28" t="n">
         <v>55100000</v>
       </c>
-      <c r="I101" s="37" t="n">
+      <c r="I101" s="28" t="n">
         <v>6900000</v>
       </c>
-      <c r="J101" s="37" t="n">
+      <c r="J101" s="28" t="n">
         <v>74900</v>
       </c>
-      <c r="K101" s="37" t="n">
+      <c r="K101" s="28" t="n">
         <v>118100</v>
       </c>
-      <c r="L101" s="37">
+      <c r="L101" s="28">
         <f>I101+J101+K101</f>
         <v/>
       </c>
@@ -10591,45 +9933,45 @@
       <c r="A102" s="25" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="39" t="inlineStr">
+      <c r="B102" s="30" t="inlineStr">
         <is>
           <t>@dj_k9hondo</t>
         </is>
       </c>
-      <c r="C102" s="39" t="inlineStr">
+      <c r="C102" s="30" t="inlineStr">
         <is>
           <t>dj_k9hondo</t>
         </is>
       </c>
-      <c r="D102" s="39" t="inlineStr">
+      <c r="D102" s="30" t="inlineStr">
         <is>
           <t>Talents &amp; Créativité</t>
         </is>
       </c>
-      <c r="E102" s="39" t="inlineStr">
+      <c r="E102" s="30" t="inlineStr">
         <is>
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F102" s="40" t="n">
+      <c r="F102" s="31" t="n">
         <v>958100</v>
       </c>
       <c r="G102" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="H102" s="40" t="n">
+      <c r="H102" s="31" t="n">
         <v>27700000</v>
       </c>
-      <c r="I102" s="40" t="n">
+      <c r="I102" s="31" t="n">
         <v>6900000</v>
       </c>
-      <c r="J102" s="40" t="n">
+      <c r="J102" s="31" t="n">
         <v>34800</v>
       </c>
-      <c r="K102" s="40" t="n">
+      <c r="K102" s="31" t="n">
         <v>224600</v>
       </c>
-      <c r="L102" s="40">
+      <c r="L102" s="31">
         <f>I102+J102+K102</f>
         <v/>
       </c>
@@ -10676,25 +10018,25 @@
           <t>Micro/Nano (&lt;1M)</t>
         </is>
       </c>
-      <c r="F103" s="37" t="n">
+      <c r="F103" s="28" t="n">
         <v>830400</v>
       </c>
       <c r="G103" s="20" t="n">
         <v>39</v>
       </c>
-      <c r="H103" s="37" t="n">
+      <c r="H103" s="28" t="n">
         <v>58400000</v>
       </c>
-      <c r="I103" s="37" t="n">
+      <c r="I103" s="28" t="n">
         <v>6800000</v>
       </c>
-      <c r="J103" s="37" t="n">
+      <c r="J103" s="28" t="n">
         <v>71100</v>
       </c>
-      <c r="K103" s="37" t="n">
+      <c r="K103" s="28" t="n">
         <v>205700</v>
       </c>
-      <c r="L103" s="37">
+      <c r="L103" s="28">
         <f>I103+J103+K103</f>
         <v/>
       </c>
@@ -10721,45 +10063,45 @@
       <c r="A104" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="39" t="inlineStr">
+      <c r="B104" s="30" t="inlineStr">
         <is>
           <t>@pol.fam</t>
         </is>
       </c>
-      <c r="C104" s="39" t="inlineStr">
+      <c r="C104" s="30" t="inlineStr">
         <is>
           <t>Семья Полиенко</t>
         </is>
       </c>
-      <c r="D104" s="39" t="inlineStr">
+      <c r="D104" s="30" t="inlineStr">
         <is>
           <t>Animaux &amp; Pets</t>
         </is>
       </c>
-      <c r="E104" s="39" t="inlineStr">
+      <c r="E104" s="30" t="inlineStr">
         <is>
           <t>Mid/Macro (1M-5M)</t>
         </is>
       </c>
-      <c r="F104" s="40" t="n">
+      <c r="F104" s="31" t="n">
         <v>1500000</v>
       </c>
       <c r="G104" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="H104" s="40" t="n">
+      <c r="H104" s="31" t="n">
         <v>161300000</v>
       </c>
-      <c r="I104" s="40" t="n">
+      <c r="I104" s="31" t="n">
         <v>6800000</v>
       </c>
-      <c r="J104" s="40" t="n">
+      <c r="J104" s="31" t="n">
         <v>31600</v>
       </c>
-      <c r="K104" s="40" t="n">
+      <c r="K104" s="31" t="n">
         <v>46700</v>
       </c>
-      <c r="L104" s="40">
+      <c r="L104" s="31">
         <f>I104+J104+K104</f>
         <v/>
       </c>
